--- a/research/traditional_assets/database/data/turkey/turkey_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ26"/>
+  <dimension ref="A1:AQ29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0668</v>
+        <v>0.193</v>
       </c>
       <c r="E2">
-        <v>0.6479999999999999</v>
+        <v>0.724</v>
       </c>
       <c r="G2">
-        <v>0.02124632046395175</v>
+        <v>0.03109819861087577</v>
       </c>
       <c r="H2">
-        <v>0.02095248125393119</v>
+        <v>0.03069169754066853</v>
       </c>
       <c r="I2">
-        <v>0.03302345418755786</v>
+        <v>0.05364774038709477</v>
       </c>
       <c r="J2">
-        <v>0.03098945587812062</v>
+        <v>0.04966112552953437</v>
       </c>
       <c r="K2">
-        <v>699.604</v>
+        <v>546.278</v>
       </c>
       <c r="L2">
-        <v>0.203535729393289</v>
+        <v>0.2367405028045541</v>
       </c>
       <c r="M2">
-        <v>6.883999999999999</v>
+        <v>11.248</v>
       </c>
       <c r="N2">
-        <v>0.006097755416585469</v>
+        <v>0.004747594124599022</v>
       </c>
       <c r="O2">
-        <v>0.009839852259278104</v>
+        <v>0.02059024892087911</v>
       </c>
       <c r="P2">
-        <v>4.553999999999999</v>
+        <v>4.298999999999999</v>
       </c>
       <c r="Q2">
-        <v>0.004033872482151398</v>
+        <v>0.001814536552422759</v>
       </c>
       <c r="R2">
-        <v>0.006509396744443998</v>
+        <v>0.007869619497764872</v>
       </c>
       <c r="S2">
-        <v>2.33</v>
+        <v>6.949000000000001</v>
       </c>
       <c r="T2">
-        <v>0.3384660081348054</v>
+        <v>0.617798719772404</v>
       </c>
       <c r="U2">
-        <v>144.864</v>
+        <v>137.546</v>
       </c>
       <c r="V2">
-        <v>0.1283185997484366</v>
+        <v>0.05805588384264731</v>
       </c>
       <c r="W2">
-        <v>0.1682568007880579</v>
+        <v>0.2642857142857143</v>
       </c>
       <c r="X2">
-        <v>0.08311488986431698</v>
+        <v>0.1363742241539245</v>
       </c>
       <c r="Y2">
-        <v>0.0851419109237409</v>
+        <v>0.1279114901317898</v>
       </c>
       <c r="Z2">
-        <v>3.9182238090027</v>
+        <v>1.487363357378266</v>
       </c>
       <c r="AA2">
-        <v>0.06857796331255674</v>
+        <v>0.1133302368787738</v>
       </c>
       <c r="AB2">
-        <v>0.08307430516177698</v>
+        <v>0.1363370919718991</v>
       </c>
       <c r="AC2">
-        <v>-0.01517941099723524</v>
+        <v>-0.02301738765430233</v>
       </c>
       <c r="AD2">
-        <v>249.608</v>
+        <v>277.497</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>249.608</v>
+        <v>277.497</v>
       </c>
       <c r="AG2">
-        <v>104.744</v>
+        <v>139.951</v>
       </c>
       <c r="AH2">
-        <v>0.1810658751091729</v>
+        <v>0.1048465313558749</v>
       </c>
       <c r="AI2">
-        <v>0.1485111284580089</v>
+        <v>0.1685164200531242</v>
       </c>
       <c r="AJ2">
-        <v>0.08490342745792277</v>
+        <v>0.0557762366633176</v>
       </c>
       <c r="AK2">
-        <v>0.06819839153262773</v>
+        <v>0.09273436878793502</v>
       </c>
       <c r="AL2">
-        <v>38.863</v>
+        <v>33.568</v>
       </c>
       <c r="AM2">
-        <v>28.924</v>
+        <v>-41.44</v>
       </c>
       <c r="AN2">
-        <v>2.182918510485719</v>
+        <v>2.200750245852235</v>
       </c>
       <c r="AO2">
-        <v>2.920772971721175</v>
+        <v>3.687797902764538</v>
       </c>
       <c r="AP2">
-        <v>0.9160267958651811</v>
+        <v>1.109911810424135</v>
       </c>
       <c r="AQ2">
-        <v>3.924422624809847</v>
+        <v>-2.987258687258687</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hedef Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HDFGS)</t>
+          <t>Hedef Holding A.S (IBSE:HEDEF)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,38 +721,32 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E3">
-        <v>1.649</v>
-      </c>
       <c r="G3">
-        <v>0.8238095238095239</v>
+        <v>0.1442786069651741</v>
       </c>
       <c r="H3">
-        <v>0.8238095238095239</v>
+        <v>0.1442786069651741</v>
       </c>
       <c r="I3">
-        <v>0.9547619047619048</v>
+        <v>0.9875621890547264</v>
       </c>
       <c r="J3">
-        <v>0.9547619047619048</v>
+        <v>0.805411829740188</v>
       </c>
       <c r="K3">
-        <v>42</v>
+        <v>33.1</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0.8233830845771144</v>
       </c>
       <c r="M3">
-        <v>2.33</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.04213381555153707</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.05547619047619048</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -764,79 +758,61 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>2.33</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1.56</v>
+        <v>0.068</v>
       </c>
       <c r="V3">
-        <v>0.02820976491862568</v>
-      </c>
-      <c r="W3">
-        <v>1.438356164383562</v>
+        <v>0.0001846320934021179</v>
       </c>
       <c r="X3">
-        <v>0.08313104729622117</v>
-      </c>
-      <c r="Y3">
-        <v>1.35522511708734</v>
-      </c>
-      <c r="Z3">
-        <v>1.780264496439471</v>
-      </c>
-      <c r="AA3">
-        <v>1.699728721600543</v>
+        <v>0.13630562891089</v>
       </c>
       <c r="AB3">
-        <v>0.08308353245022176</v>
-      </c>
-      <c r="AC3">
-        <v>1.616645189150321</v>
+        <v>0.1362990775494417</v>
       </c>
       <c r="AD3">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="AG3">
-        <v>-1.447</v>
+        <v>0.013</v>
       </c>
       <c r="AH3">
-        <v>0.002039232671033873</v>
+        <v>0.000219881047068117</v>
       </c>
       <c r="AI3">
-        <v>0.001396561739151929</v>
+        <v>0.001142760401235874</v>
       </c>
       <c r="AJ3">
-        <v>-0.02686944088537315</v>
+        <v>3.529606611767708e-05</v>
       </c>
       <c r="AK3">
-        <v>-0.01823497536325029</v>
+        <v>0.0001835821106294042</v>
       </c>
       <c r="AL3">
-        <v>0.008999999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="AM3">
-        <v>-1.871</v>
+        <v>-0.778</v>
       </c>
       <c r="AN3">
-        <v>0.002817955112219451</v>
+        <v>0.002040302267002519</v>
       </c>
       <c r="AO3">
-        <v>4455.555555555556</v>
+        <v>1368.965517241379</v>
       </c>
       <c r="AP3">
-        <v>-0.03608478802992519</v>
+        <v>0.0003274559193954659</v>
       </c>
       <c r="AQ3">
-        <v>-21.43238909673971</v>
+        <v>-51.02827763496144</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Güler Yatirim Holding A.S. (IBSE:GLRYH)</t>
+          <t>Atlantis Yatirim Holding A.S. (IBSE:ATSYH)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,28 +832,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>1.498</v>
-      </c>
-      <c r="E4">
-        <v>0.828</v>
+        <v>0.337</v>
       </c>
       <c r="G4">
-        <v>0.02996896505194981</v>
+        <v>0.007604562737642586</v>
       </c>
       <c r="H4">
-        <v>0.02860612602887599</v>
+        <v>0.007604562737642586</v>
       </c>
       <c r="I4">
-        <v>0.04196464714613413</v>
+        <v>0.2064638783269962</v>
       </c>
       <c r="J4">
-        <v>0.03295545366790813</v>
+        <v>0.1428871319681389</v>
       </c>
       <c r="K4">
-        <v>9.9</v>
+        <v>0.333</v>
       </c>
       <c r="L4">
-        <v>0.01335852111725813</v>
+        <v>0.1266159695817491</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -901,73 +874,61 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>16.7</v>
+        <v>0.003</v>
       </c>
       <c r="V4">
-        <v>0.6788617886178862</v>
+        <v>6e-05</v>
       </c>
       <c r="W4">
-        <v>0.7333333333333334</v>
+        <v>0.6529411764705882</v>
       </c>
       <c r="X4">
-        <v>0.1247659788386524</v>
+        <v>0.1362906208857788</v>
       </c>
       <c r="Y4">
-        <v>0.6085673544946809</v>
-      </c>
-      <c r="Z4">
-        <v>30.93717386766854</v>
-      </c>
-      <c r="AA4">
-        <v>1.019548600011969</v>
+        <v>0.5166505555848095</v>
       </c>
       <c r="AB4">
-        <v>0.099563590895135</v>
-      </c>
-      <c r="AC4">
-        <v>0.9199850091168339</v>
+        <v>0.136290025297337</v>
       </c>
       <c r="AD4">
-        <v>18.9</v>
+        <v>0.001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>18.9</v>
+        <v>0.001</v>
       </c>
       <c r="AG4">
-        <v>2.199999999999999</v>
+        <v>-0.002</v>
       </c>
       <c r="AH4">
-        <v>0.4344827586206896</v>
+        <v>1.999960000799984e-05</v>
       </c>
       <c r="AI4">
-        <v>0.2386363636363636</v>
+        <v>0.001328021248339974</v>
       </c>
       <c r="AJ4">
-        <v>0.08208955223880594</v>
+        <v>-4.000160006400256e-05</v>
       </c>
       <c r="AK4">
-        <v>0.03519999999999999</v>
+        <v>-0.002666666666666667</v>
       </c>
       <c r="AL4">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>2.34</v>
+        <v>-0.109</v>
       </c>
       <c r="AN4">
-        <v>0.6</v>
-      </c>
-      <c r="AO4">
-        <v>6.702586206896552</v>
+        <v>0.001814882032667877</v>
       </c>
       <c r="AP4">
-        <v>0.06984126984126982</v>
+        <v>-0.003629764065335753</v>
       </c>
       <c r="AQ4">
-        <v>13.29059829059829</v>
+        <v>-4.98165137614679</v>
       </c>
     </row>
     <row r="5">
@@ -978,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Denge Yatirim Holding A.S. (IBSE:DENGE)</t>
+          <t>Euro Menkul Kiymet Yatirim Ortakligi Anonim Sirketi (IBSE:EUYO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -987,118 +948,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.725</v>
+        <v>-0.244</v>
       </c>
       <c r="E5">
-        <v>0.305</v>
+        <v>0.201</v>
       </c>
       <c r="G5">
-        <v>0.04891089108910891</v>
+        <v>0.08950617283950615</v>
       </c>
       <c r="H5">
-        <v>0.04891089108910891</v>
+        <v>0.08950617283950615</v>
       </c>
       <c r="I5">
-        <v>0.09306930693069307</v>
+        <v>0.1080246913580247</v>
       </c>
       <c r="J5">
-        <v>0.09306930693069307</v>
+        <v>0.1080246913580247</v>
       </c>
       <c r="K5">
-        <v>4.2</v>
+        <v>0.321</v>
       </c>
       <c r="L5">
-        <v>0.2079207920792079</v>
+        <v>0.09907407407407406</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>0.038</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.007421875</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.1183800623052959</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>0.038</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.007421875</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.1183800623052959</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
       <c r="U5">
-        <v>14.3</v>
+        <v>2.01</v>
       </c>
       <c r="V5">
-        <v>0.4914089347079038</v>
+        <v>0.3925781249999999</v>
       </c>
       <c r="W5">
-        <v>1.079691516709512</v>
+        <v>0.07262443438914028</v>
       </c>
       <c r="X5">
-        <v>0.1608829645501768</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y5">
-        <v>0.9188085521593348</v>
+        <v>-0.06366468516419733</v>
       </c>
       <c r="Z5">
-        <v>5.422818791946308</v>
+        <v>14.72727272727274</v>
       </c>
       <c r="AA5">
-        <v>0.5046979865771811</v>
+        <v>1.590909090909093</v>
       </c>
       <c r="AB5">
-        <v>0.1013648887013059</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC5">
-        <v>0.4033330978758752</v>
+        <v>1.454619971355755</v>
       </c>
       <c r="AD5">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>41.7</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>27.4</v>
+        <v>-2.01</v>
       </c>
       <c r="AH5">
-        <v>0.5889830508474576</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.4398734177215189</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>0.4849557522123894</v>
+        <v>-0.6463022508038584</v>
       </c>
       <c r="AK5">
-        <v>0.3403726708074534</v>
+        <v>-5.153846153846152</v>
       </c>
       <c r="AL5">
-        <v>0.604</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.408</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>17.52100840336135</v>
-      </c>
-      <c r="AO5">
-        <v>3.112582781456954</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>11.51260504201681</v>
-      </c>
-      <c r="AQ5">
-        <v>4.607843137254902</v>
+        <v>-5.726495726495727</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vakif Menkul Kiymet Yatirim Ortakligi A.S. (IBSE:VKFYO)</t>
+          <t>Euro Kapital Yatirim Ortakligi Anonim Sirketi (IBSE:EUKYO)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,100 +1076,103 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06309999999999999</v>
+        <v>-0.28</v>
       </c>
       <c r="E6">
-        <v>1.308</v>
+        <v>0.17</v>
       </c>
       <c r="G6">
-        <v>0.003708609271523179</v>
+        <v>0.09205298013245033</v>
       </c>
       <c r="H6">
-        <v>0.003708609271523179</v>
+        <v>0.09205298013245033</v>
       </c>
       <c r="I6">
-        <v>0.02443708609271523</v>
+        <v>0.1043046357615894</v>
       </c>
       <c r="J6">
-        <v>0.02443708609271523</v>
+        <v>0.1043046357615894</v>
       </c>
       <c r="K6">
-        <v>0.369</v>
+        <v>0.314</v>
       </c>
       <c r="L6">
-        <v>0.02443708609271523</v>
+        <v>0.1039735099337748</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.038</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.007169811320754717</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.1210191082802548</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.038</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.007169811320754717</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.1210191082802548</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>0.915</v>
+        <v>2.07</v>
       </c>
       <c r="V6">
-        <v>0.07261904761904762</v>
+        <v>0.390566037735849</v>
       </c>
       <c r="W6">
-        <v>0.1013736263736264</v>
+        <v>0.06796536796536796</v>
       </c>
       <c r="X6">
-        <v>0.08302864186958671</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y6">
-        <v>0.01834498450403967</v>
+        <v>-0.06832375158796965</v>
       </c>
       <c r="Z6">
-        <v>13.32744924977934</v>
+        <v>14.38095238095238</v>
       </c>
       <c r="AA6">
-        <v>0.3256840247131508</v>
+        <v>1.5</v>
       </c>
       <c r="AB6">
-        <v>0.08302534706365212</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC6">
-        <v>0.2426586776494987</v>
+        <v>1.363710880446663</v>
       </c>
       <c r="AD6">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-0.913</v>
+        <v>-2.07</v>
       </c>
       <c r="AH6">
-        <v>0.0001587049674654817</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.0005662514156285391</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.07812098913322496</v>
+        <v>-0.6408668730650154</v>
       </c>
       <c r="AK6">
-        <v>-0.3488727550630493</v>
+        <v>-5.048780487804876</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1220,10 +1181,10 @@
         <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.005390835579514825</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>-2.460916442048517</v>
+        <v>-6.489028213166144</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1195,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Euro Menkul Kiymet Yatirim Ortakligi Anonim Sirketi (IBSE:EUYO)</t>
+          <t>Euro Trend Yatirim Ortakligi A.S. (IBSE:ETYAT)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1243,43 +1204,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.125</v>
+        <v>-0.254</v>
+      </c>
+      <c r="E7">
+        <v>0.186</v>
       </c>
       <c r="G7">
-        <v>0.04336585365853659</v>
+        <v>0.07408536585365853</v>
       </c>
       <c r="H7">
-        <v>0.04336585365853659</v>
+        <v>0.07408536585365853</v>
       </c>
       <c r="I7">
-        <v>0.0188780487804878</v>
+        <v>0.08810975609756097</v>
       </c>
       <c r="J7">
-        <v>0.0188780487804878</v>
+        <v>0.08810975609756097</v>
       </c>
       <c r="K7">
-        <v>0.38</v>
+        <v>0.284</v>
       </c>
       <c r="L7">
-        <v>0.01853658536585366</v>
+        <v>0.08658536585365853</v>
       </c>
       <c r="M7">
-        <v>0.141</v>
+        <v>0.033</v>
       </c>
       <c r="N7">
-        <v>0.02907216494845361</v>
+        <v>0.00586145648312611</v>
       </c>
       <c r="O7">
-        <v>0.3710526315789474</v>
+        <v>0.1161971830985916</v>
       </c>
       <c r="P7">
-        <v>0.141</v>
+        <v>0.033</v>
       </c>
       <c r="Q7">
-        <v>0.02907216494845361</v>
+        <v>0.00586145648312611</v>
       </c>
       <c r="R7">
-        <v>0.3710526315789474</v>
+        <v>0.1161971830985916</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1288,31 +1252,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>4.2</v>
+        <v>1.91</v>
       </c>
       <c r="V7">
-        <v>0.8659793814432991</v>
+        <v>0.3392539964476021</v>
       </c>
       <c r="W7">
-        <v>0.07900207900207901</v>
+        <v>0.06558891454965357</v>
       </c>
       <c r="X7">
-        <v>0.08302001710550982</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y7">
-        <v>-0.004017938103430818</v>
+        <v>-0.07070020500368404</v>
       </c>
       <c r="Z7">
-        <v>13.05732484076434</v>
+        <v>16.39999999999998</v>
       </c>
       <c r="AA7">
-        <v>0.2464968152866243</v>
+        <v>1.444999999999999</v>
       </c>
       <c r="AB7">
-        <v>0.08302001710550982</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC7">
-        <v>0.1634767981811145</v>
+        <v>1.308710880446661</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1324,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-4.2</v>
+        <v>-1.91</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1333,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-6.461538461538467</v>
+        <v>-0.5134408602150538</v>
       </c>
       <c r="AK7">
-        <v>-19.09090909090911</v>
+        <v>-4.658536585365854</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1348,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>-10.82474226804124</v>
+        <v>-6.586206896551724</v>
       </c>
     </row>
     <row r="8">
@@ -1359,7 +1323,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Euro Kapital Yatirim Ortakligi Anonim Sirketi (IBSE:EUKYO)</t>
+          <t>Güler Yatirim Holding A.S. (IBSE:GLRYH)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1368,112 +1332,115 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.142</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="G8">
-        <v>0.04054726368159203</v>
+        <v>0.04514931793044119</v>
       </c>
       <c r="H8">
-        <v>0.04054726368159203</v>
+        <v>0.04399655892835197</v>
       </c>
       <c r="I8">
-        <v>0.0191044776119403</v>
+        <v>0.06697800172053582</v>
       </c>
       <c r="J8">
-        <v>0.0191044776119403</v>
+        <v>0.05585463338746064</v>
       </c>
       <c r="K8">
-        <v>0.384</v>
+        <v>21.3</v>
       </c>
       <c r="L8">
-        <v>0.0191044776119403</v>
+        <v>0.02617672360820941</v>
       </c>
       <c r="M8">
-        <v>0.129</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.02411214953271028</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.3359375</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>0.129</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.02411214953271028</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.3359375</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>4.41</v>
+        <v>13.8</v>
       </c>
       <c r="V8">
-        <v>0.8242990654205609</v>
+        <v>0.1593533487297922</v>
       </c>
       <c r="W8">
-        <v>0.07634194831013916</v>
+        <v>0.6698113207547169</v>
       </c>
       <c r="X8">
-        <v>0.08302001710550982</v>
+        <v>0.1784165771968134</v>
       </c>
       <c r="Y8">
-        <v>-0.006678068795370667</v>
+        <v>0.4913947435579036</v>
       </c>
       <c r="Z8">
-        <v>11.89349112426035</v>
+        <v>24.30188453842249</v>
       </c>
       <c r="AA8">
-        <v>0.2272189349112426</v>
+        <v>1.357372851517986</v>
       </c>
       <c r="AB8">
-        <v>0.08302001710550982</v>
+        <v>0.1515169179090169</v>
       </c>
       <c r="AC8">
-        <v>0.1441989178057327</v>
+        <v>1.205855933608969</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>48.6</v>
       </c>
       <c r="AG8">
-        <v>-4.41</v>
+        <v>34.8</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.3594674556213018</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.3441926345609065</v>
       </c>
       <c r="AJ8">
-        <v>-4.69148936170213</v>
+        <v>0.28665568369028</v>
       </c>
       <c r="AK8">
-        <v>-21</v>
+        <v>0.2731554160125589</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>0.8868613138686132</v>
+      </c>
+      <c r="AO8">
+        <v>10.09259259259259</v>
       </c>
       <c r="AP8">
-        <v>-11.27877237851662</v>
+        <v>0.635036496350365</v>
+      </c>
+      <c r="AQ8">
+        <v>165.1515151515151</v>
       </c>
     </row>
     <row r="9">
@@ -1484,7 +1451,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Euro Trend Yatirim Ortakligi A.S. (IBSE:ETYAT)</t>
+          <t>Birikim Varlik Yonetim Anonim Sirketi (IBSE:BRKVY)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1492,113 +1459,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>-0.122</v>
-      </c>
       <c r="G9">
-        <v>0.04316326530612245</v>
+        <v>0.4906832298136646</v>
       </c>
       <c r="H9">
-        <v>0.04316326530612245</v>
+        <v>0.4906832298136646</v>
       </c>
       <c r="I9">
-        <v>0.01724489795918367</v>
+        <v>0.5714285714285713</v>
       </c>
       <c r="J9">
-        <v>0.01724489795918367</v>
+        <v>0.4425249169435215</v>
       </c>
       <c r="K9">
-        <v>0.339</v>
+        <v>13.3</v>
       </c>
       <c r="L9">
-        <v>0.01729591836734694</v>
+        <v>0.4130434782608696</v>
       </c>
       <c r="M9">
-        <v>0.135</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.02415026833631485</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.3982300884955752</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>0.135</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.02415026833631485</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.3982300884955752</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>4.13</v>
+        <v>2.74</v>
       </c>
       <c r="V9">
-        <v>0.738819320214669</v>
+        <v>0.02582469368520264</v>
       </c>
       <c r="W9">
-        <v>0.07136842105263158</v>
+        <v>1.366906474820144</v>
       </c>
       <c r="X9">
-        <v>0.08302001710550982</v>
+        <v>0.1424232158137158</v>
       </c>
       <c r="Y9">
-        <v>-0.01165159605287824</v>
+        <v>1.224483259006428</v>
       </c>
       <c r="Z9">
-        <v>12.81045751633987</v>
+        <v>1.758601856908793</v>
       </c>
       <c r="AA9">
-        <v>0.2209150326797386</v>
+        <v>0.7782251406652863</v>
       </c>
       <c r="AB9">
-        <v>0.08302001710550982</v>
+        <v>0.1397102912579481</v>
       </c>
       <c r="AC9">
-        <v>0.1378950155742288</v>
+        <v>0.6385148494073382</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>8.67</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>8.67</v>
       </c>
       <c r="AG9">
-        <v>-4.13</v>
+        <v>5.93</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.07554238912607825</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.3202807536017732</v>
       </c>
       <c r="AJ9">
-        <v>-2.828767123287671</v>
+        <v>0.05293225029010086</v>
       </c>
       <c r="AK9">
-        <v>-20.64999999999998</v>
+        <v>0.2437320180846691</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.4711956521739131</v>
+      </c>
+      <c r="AO9">
+        <v>14.15384615384615</v>
       </c>
       <c r="AP9">
-        <v>-12.2189349112426</v>
+        <v>0.3222826086956522</v>
+      </c>
+      <c r="AQ9">
+        <v>14.15384615384615</v>
       </c>
     </row>
     <row r="10">
@@ -1609,7 +1576,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Oyak Yatirim Ortakligi AS (IBSE:OYAYO)</t>
+          <t>Atlas Menkul Kiymetler Yatirim Ortakligi A.S. (IBSE:ATLAS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1618,46 +1585,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.057</v>
+        <v>0.0525</v>
       </c>
       <c r="E10">
-        <v>0.468</v>
+        <v>0.531</v>
       </c>
       <c r="G10">
-        <v>0.08574686431014823</v>
+        <v>0.02061440677966101</v>
       </c>
       <c r="H10">
-        <v>0.08574686431014823</v>
+        <v>0.02061440677966101</v>
       </c>
       <c r="I10">
-        <v>0.08141391106043329</v>
+        <v>0.06673728813559321</v>
       </c>
       <c r="J10">
-        <v>0.08141391106043329</v>
+        <v>0.06673728813559321</v>
       </c>
       <c r="K10">
-        <v>0.714</v>
+        <v>3.13</v>
       </c>
       <c r="L10">
-        <v>0.08141391106043329</v>
+        <v>0.06631355932203389</v>
       </c>
       <c r="M10">
-        <v>0.119</v>
+        <v>0.127</v>
       </c>
       <c r="N10">
-        <v>0.01155339805825243</v>
+        <v>0.01104347826086957</v>
       </c>
       <c r="O10">
-        <v>0.1666666666666667</v>
+        <v>0.04057507987220448</v>
       </c>
       <c r="P10">
-        <v>0.119</v>
+        <v>0.127</v>
       </c>
       <c r="Q10">
-        <v>0.01155339805825243</v>
+        <v>0.01104347826086957</v>
       </c>
       <c r="R10">
-        <v>0.1666666666666667</v>
+        <v>0.04057507987220448</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1666,31 +1633,31 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.392</v>
+        <v>3.27</v>
       </c>
       <c r="V10">
-        <v>0.03805825242718446</v>
+        <v>0.2843478260869565</v>
       </c>
       <c r="W10">
-        <v>0.1720481927710843</v>
+        <v>0.343956043956044</v>
       </c>
       <c r="X10">
-        <v>0.08302001710550982</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y10">
-        <v>0.0890281756655745</v>
+        <v>0.2076669244027063</v>
       </c>
       <c r="Z10">
-        <v>2.150564001961746</v>
+        <v>11.37349397590362</v>
       </c>
       <c r="AA10">
-        <v>0.1750858263854831</v>
+        <v>0.7590361445783134</v>
       </c>
       <c r="AB10">
-        <v>0.08302001710550982</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC10">
-        <v>0.09206580927997324</v>
+        <v>0.6227470250249758</v>
       </c>
       <c r="AD10">
         <v>0</v>
@@ -1702,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="AG10">
-        <v>-0.392</v>
+        <v>-3.27</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -1711,16 +1678,22 @@
         <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-0.03956398869600323</v>
+        <v>-0.3973268529769137</v>
       </c>
       <c r="AK10">
-        <v>-0.1029411764705882</v>
+        <v>-0.7995110024449879</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
         <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>-1.038095238095238</v>
       </c>
     </row>
     <row r="11">
@@ -1731,7 +1704,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Verusaturk Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:VERTU)</t>
+          <t>Metro Yatirim Ortakligi A.S. (IBSE:MTRYO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1739,29 +1712,47 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D11">
+        <v>0.611</v>
+      </c>
       <c r="E11">
-        <v>0.905</v>
+        <v>0.7709999999999999</v>
+      </c>
+      <c r="G11">
+        <v>0.02004739336492891</v>
+      </c>
+      <c r="H11">
+        <v>0.02004739336492891</v>
+      </c>
+      <c r="I11">
+        <v>0.07440758293838862</v>
+      </c>
+      <c r="J11">
+        <v>0.07440758293838862</v>
       </c>
       <c r="K11">
-        <v>83.3</v>
+        <v>3.14</v>
+      </c>
+      <c r="L11">
+        <v>0.07440758293838862</v>
       </c>
       <c r="M11">
-        <v>0.293</v>
+        <v>0.126</v>
       </c>
       <c r="N11">
-        <v>0.003011305241521069</v>
+        <v>0.01461716937354988</v>
       </c>
       <c r="O11">
-        <v>0.003517406962785114</v>
+        <v>0.04012738853503185</v>
       </c>
       <c r="P11">
-        <v>0.293</v>
+        <v>0.126</v>
       </c>
       <c r="Q11">
-        <v>0.003011305241521069</v>
+        <v>0.01461716937354988</v>
       </c>
       <c r="R11">
-        <v>0.003517406962785114</v>
+        <v>0.04012738853503185</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1770,73 +1761,67 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.473</v>
+        <v>3.14</v>
       </c>
       <c r="V11">
-        <v>0.00486125385405961</v>
+        <v>0.3642691415313226</v>
       </c>
       <c r="W11">
-        <v>2.61128526645768</v>
+        <v>0.3442982456140351</v>
       </c>
       <c r="X11">
-        <v>0.08594623202541009</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y11">
-        <v>2.52533903443227</v>
+        <v>0.2080091260606975</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>10.04761904761905</v>
       </c>
       <c r="AA11">
-        <v>0.1512890094979647</v>
+        <v>0.7476190476190477</v>
       </c>
       <c r="AB11">
-        <v>0.08461167545888973</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC11">
-        <v>0.066677334039075</v>
+        <v>0.6113299280657101</v>
       </c>
       <c r="AD11">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>4.767</v>
+        <v>-3.14</v>
       </c>
       <c r="AH11">
-        <v>0.05110200897210845</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.04477101845522899</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>0.04670461559563817</v>
+        <v>-0.5729927007299271</v>
       </c>
       <c r="AK11">
-        <v>0.0408949359595769</v>
+        <v>-0.7388235294117648</v>
       </c>
       <c r="AL11">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.203</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>1.174887892376682</v>
-      </c>
-      <c r="AO11">
-        <v>5.946666666666666</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.068834080717489</v>
-      </c>
-      <c r="AQ11">
-        <v>21.9704433497537</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12">
@@ -1847,7 +1832,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Is Yatirim Ortakligi A.S. (IBSE:ISYAT)</t>
+          <t>Oyak Yatirim Ortakligi AS (IBSE:OYAYO)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1856,46 +1841,46 @@
         </is>
       </c>
       <c r="D12">
-        <v>-0.09910000000000001</v>
+        <v>0.169</v>
       </c>
       <c r="E12">
-        <v>0.0989</v>
+        <v>0.677</v>
       </c>
       <c r="G12">
-        <v>0.121474358974359</v>
+        <v>0.04176991150442477</v>
       </c>
       <c r="H12">
-        <v>0.121474358974359</v>
+        <v>0.04176991150442477</v>
       </c>
       <c r="I12">
-        <v>0.1150641025641026</v>
+        <v>0.09823008849557523</v>
       </c>
       <c r="J12">
-        <v>0.1150641025641026</v>
+        <v>0.09823008849557523</v>
       </c>
       <c r="K12">
-        <v>3.57</v>
+        <v>1.11</v>
       </c>
       <c r="L12">
-        <v>0.1144230769230769</v>
+        <v>0.09823008849557523</v>
       </c>
       <c r="M12">
-        <v>2.82</v>
+        <v>0.063</v>
       </c>
       <c r="N12">
-        <v>0.07268041237113403</v>
+        <v>0.00443661971830986</v>
       </c>
       <c r="O12">
-        <v>0.7899159663865546</v>
+        <v>0.05675675675675675</v>
       </c>
       <c r="P12">
-        <v>2.82</v>
+        <v>0.063</v>
       </c>
       <c r="Q12">
-        <v>0.07268041237113403</v>
+        <v>0.00443661971830986</v>
       </c>
       <c r="R12">
-        <v>0.7899159663865546</v>
+        <v>0.05675675675675675</v>
       </c>
       <c r="S12">
         <v>0</v>
@@ -1904,73 +1889,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>4.72</v>
+        <v>0.354</v>
       </c>
       <c r="V12">
-        <v>0.1216494845360825</v>
+        <v>0.02492957746478873</v>
       </c>
       <c r="W12">
-        <v>0.1144230769230769</v>
+        <v>0.2642857142857143</v>
       </c>
       <c r="X12">
-        <v>0.08310824310711079</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="Y12">
-        <v>0.03131483381596613</v>
+        <v>0.1279965947323767</v>
       </c>
       <c r="Z12">
-        <v>1.007751937984496</v>
+        <v>2.967436974789916</v>
       </c>
       <c r="AA12">
-        <v>0.1159560723514212</v>
+        <v>0.2914915966386555</v>
       </c>
       <c r="AB12">
-        <v>0.08307050835356794</v>
+        <v>0.1362891195533376</v>
       </c>
       <c r="AC12">
-        <v>0.03288556399785324</v>
+        <v>0.1552024770853179</v>
       </c>
       <c r="AD12">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0.063</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>-4.657</v>
+        <v>-0.354</v>
       </c>
       <c r="AH12">
-        <v>0.001621079175565448</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.00226106305853641</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>-0.1363969188413438</v>
+        <v>-0.02556695074389715</v>
       </c>
       <c r="AK12">
-        <v>-0.2012271529188091</v>
+        <v>-0.130820399113082</v>
       </c>
       <c r="AL12">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="AN12">
-        <v>0.01754874651810585</v>
-      </c>
-      <c r="AO12">
-        <v>188.9473684210526</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>-1.297214484679666</v>
-      </c>
-      <c r="AQ12">
-        <v>188.9473684210526</v>
+        <v>-0.3189189189189189</v>
       </c>
     </row>
     <row r="13">
@@ -1981,7 +1960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Atlas Menkul Kiymetler Yatirim Ortakligi A.S. (IBSE:ATLAS)</t>
+          <t>Deniz Gayrimenkul Yatirim Ortakligi A.S. (IBSE:DZGYO)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1990,112 +1969,118 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.254</v>
+        <v>1.284</v>
+      </c>
+      <c r="E13">
+        <v>0.862</v>
       </c>
       <c r="G13">
-        <v>0.01810650887573964</v>
+        <v>0.2719298245614035</v>
       </c>
       <c r="H13">
-        <v>0.01810650887573964</v>
+        <v>0.2719298245614035</v>
       </c>
       <c r="I13">
-        <v>0.00816568047337278</v>
+        <v>0.3991228070175438</v>
       </c>
       <c r="J13">
-        <v>0.00816568047337278</v>
+        <v>0.3991228070175438</v>
       </c>
       <c r="K13">
-        <v>0.407</v>
+        <v>18.4</v>
       </c>
       <c r="L13">
-        <v>0.008027613412228796</v>
+        <v>0.4035087719298245</v>
       </c>
       <c r="M13">
-        <v>0.144</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.0259927797833935</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>0.3538083538083538</v>
+        <v>-0</v>
       </c>
       <c r="P13">
-        <v>0.144</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.0259927797833935</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>0.3538083538083538</v>
+        <v>-0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>4.95</v>
+        <v>19.3</v>
       </c>
       <c r="V13">
-        <v>0.8935018050541517</v>
+        <v>0.2218390804597701</v>
       </c>
       <c r="W13">
-        <v>0.03990196078431373</v>
+        <v>0.2555555555555555</v>
       </c>
       <c r="X13">
-        <v>0.08302001710550982</v>
+        <v>0.1364030137385261</v>
       </c>
       <c r="Y13">
-        <v>-0.0431180563211961</v>
+        <v>0.1191525418170294</v>
       </c>
       <c r="Z13">
-        <v>13.85245901639345</v>
+        <v>0.7078656917990035</v>
       </c>
       <c r="AA13">
-        <v>0.1131147540983607</v>
+        <v>0.2825253419022338</v>
       </c>
       <c r="AB13">
-        <v>0.08302001710550982</v>
+        <v>0.1363577284450676</v>
       </c>
       <c r="AC13">
-        <v>0.03009473699285085</v>
+        <v>0.1461676134571663</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>0.132</v>
       </c>
       <c r="AG13">
-        <v>-4.95</v>
+        <v>-19.168</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.001514942845338108</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>0.00248906320712023</v>
       </c>
       <c r="AJ13">
-        <v>-8.389830508474578</v>
+        <v>-0.2825804929826631</v>
       </c>
       <c r="AK13">
-        <v>-1.19277108433735</v>
+        <v>-0.568243804102929</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>0.007173913043478261</v>
+      </c>
+      <c r="AO13">
+        <v>5.260115606936416</v>
       </c>
       <c r="AP13">
-        <v>-11.95652173913044</v>
+        <v>-1.041739130434783</v>
+      </c>
+      <c r="AQ13">
+        <v>16.3963963963964</v>
       </c>
     </row>
     <row r="14">
@@ -2106,7 +2091,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Verusa Holding A.S. (IBSE:VERUS)</t>
+          <t>Marka Yatirim Holding A.S. (IBSE:MARKA)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2115,121 +2100,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.0276</v>
+        <v>0.482</v>
       </c>
       <c r="E14">
-        <v>0.365</v>
+        <v>0.268</v>
       </c>
       <c r="G14">
-        <v>0.6328293736501081</v>
+        <v>-0.50873786407767</v>
       </c>
       <c r="H14">
-        <v>0.6328293736501081</v>
+        <v>-0.50873786407767</v>
       </c>
       <c r="I14">
-        <v>0.4503239740820734</v>
+        <v>0.2631067961165049</v>
       </c>
       <c r="J14">
-        <v>0.4371677514945562</v>
+        <v>0.2041012278697887</v>
       </c>
       <c r="K14">
-        <v>23.2</v>
+        <v>0.259</v>
       </c>
       <c r="L14">
-        <v>2.505399568034557</v>
+        <v>0.2514563106796117</v>
       </c>
       <c r="M14">
-        <v>0.158</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.0005741279069767443</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.006810344827586207</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>0.158</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.0005741279069767443</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.006810344827586207</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>4.72</v>
+        <v>0.068</v>
       </c>
       <c r="V14">
-        <v>0.01715116279069768</v>
+        <v>0.01207815275310835</v>
       </c>
       <c r="W14">
-        <v>0.4884210526315789</v>
+        <v>0.1497109826589595</v>
       </c>
       <c r="X14">
-        <v>0.08542880840983313</v>
+        <v>0.1366357860139873</v>
       </c>
       <c r="Y14">
-        <v>0.4029922442217458</v>
+        <v>0.01307519664497223</v>
       </c>
       <c r="Z14">
-        <v>0.166546762589928</v>
+        <v>1.154708520179372</v>
       </c>
       <c r="AA14">
-        <v>0.07280887372013652</v>
+        <v>0.2356774268003165</v>
       </c>
       <c r="AB14">
-        <v>0.0843421799422204</v>
+        <v>0.1364838534197728</v>
       </c>
       <c r="AC14">
-        <v>-0.01153330622208389</v>
+        <v>0.09919357338054374</v>
       </c>
       <c r="AD14">
-        <v>12.2</v>
+        <v>0.026</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>12.2</v>
+        <v>0.026</v>
       </c>
       <c r="AG14">
-        <v>7.48</v>
+        <v>-0.04200000000000001</v>
       </c>
       <c r="AH14">
-        <v>0.04244954766875435</v>
+        <v>0.004596888260254597</v>
       </c>
       <c r="AI14">
-        <v>0.112962962962963</v>
+        <v>0.02394106813996317</v>
       </c>
       <c r="AJ14">
-        <v>0.0264610159898118</v>
+        <v>-0.007516105941302793</v>
       </c>
       <c r="AK14">
-        <v>0.07242447714949651</v>
+        <v>-0.04125736738703341</v>
       </c>
       <c r="AL14">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1.24</v>
+        <v>-0.005</v>
       </c>
       <c r="AN14">
-        <v>2.663755458515284</v>
-      </c>
-      <c r="AO14">
-        <v>1.648221343873518</v>
+        <v>0.08843537414965986</v>
       </c>
       <c r="AP14">
-        <v>1.633187772925764</v>
+        <v>-0.1428571428571429</v>
       </c>
       <c r="AQ14">
-        <v>3.362903225806452</v>
+        <v>-54.2</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2219,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deniz Gayrimenkul Yatirim Ortakligi A.S. (IBSE:DZGYO)</t>
+          <t>Is Yatirim Ortakligi A.S. (IBSE:ISYAT)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2249,118 +2228,121 @@
         </is>
       </c>
       <c r="D15">
-        <v>1.248</v>
+        <v>-0.124</v>
       </c>
       <c r="E15">
-        <v>0.142</v>
+        <v>0.261</v>
       </c>
       <c r="G15">
-        <v>0.01114799446749654</v>
+        <v>0.2156424581005587</v>
       </c>
       <c r="H15">
-        <v>0.01114799446749654</v>
+        <v>0.2156424581005587</v>
       </c>
       <c r="I15">
-        <v>0.0760719225449516</v>
+        <v>0.2418994413407821</v>
       </c>
       <c r="J15">
-        <v>0.0760719225449516</v>
+        <v>0.2418994413407821</v>
       </c>
       <c r="K15">
-        <v>2.4</v>
+        <v>4.33</v>
       </c>
       <c r="L15">
-        <v>0.03319502074688797</v>
+        <v>0.2418994413407821</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>2.17</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.04909502262443438</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.5011547344110854</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>2.17</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.04909502262443438</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.5011547344110854</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>7.91</v>
+        <v>0.649</v>
       </c>
       <c r="V15">
-        <v>0.1097087378640777</v>
+        <v>0.01468325791855204</v>
       </c>
       <c r="W15">
-        <v>0.05031446540880503</v>
+        <v>0.1557553956834532</v>
       </c>
       <c r="X15">
-        <v>0.08326795813882702</v>
+        <v>0.1363723382067482</v>
       </c>
       <c r="Y15">
-        <v>-0.032953492730022</v>
+        <v>0.01938305747670505</v>
       </c>
       <c r="Z15">
-        <v>0.8458712590963334</v>
+        <v>0.7734520157282979</v>
       </c>
       <c r="AA15">
-        <v>0.06434705290497696</v>
+        <v>0.1870976105085771</v>
       </c>
       <c r="AB15">
-        <v>0.08317256867736354</v>
+        <v>0.1363294644691543</v>
       </c>
       <c r="AC15">
-        <v>-0.01882551577238659</v>
+        <v>0.05076814603942278</v>
       </c>
       <c r="AD15">
-        <v>0.329</v>
+        <v>0.049</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.329</v>
+        <v>0.049</v>
       </c>
       <c r="AG15">
-        <v>-7.581</v>
+        <v>-0.6</v>
       </c>
       <c r="AH15">
-        <v>0.004542379433652267</v>
+        <v>0.001107369658071369</v>
       </c>
       <c r="AI15">
-        <v>0.004548659597118722</v>
+        <v>0.003151328059682295</v>
       </c>
       <c r="AJ15">
-        <v>-0.1175002712379299</v>
+        <v>-0.01376146788990826</v>
       </c>
       <c r="AK15">
-        <v>-0.1176826712615843</v>
+        <v>-0.04026845637583892</v>
       </c>
       <c r="AL15">
-        <v>1.98</v>
+        <v>0.007</v>
       </c>
       <c r="AM15">
-        <v>1.85</v>
+        <v>0.007</v>
       </c>
       <c r="AN15">
-        <v>0.05875</v>
+        <v>0.01129032258064516</v>
       </c>
       <c r="AO15">
-        <v>2.777777777777778</v>
+        <v>618.5714285714286</v>
       </c>
       <c r="AP15">
-        <v>-1.35375</v>
+        <v>-0.1382488479262673</v>
       </c>
       <c r="AQ15">
-        <v>2.972972972972973</v>
+        <v>618.5714285714286</v>
       </c>
     </row>
     <row r="16">
@@ -2371,7 +2353,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metro Yatirim Ortakligi A.S. (IBSE:MTRYO)</t>
+          <t>Garanti Yatirim Ortakligi A.S. (IBSE:GRNYO)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2380,46 +2362,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.91</v>
+        <v>0.201</v>
       </c>
       <c r="E16">
-        <v>0.00852</v>
+        <v>0.462</v>
       </c>
       <c r="G16">
-        <v>0.008205841446453406</v>
+        <v>0.007435897435897436</v>
       </c>
       <c r="H16">
-        <v>0.008205841446453406</v>
+        <v>0.007435897435897436</v>
       </c>
       <c r="I16">
-        <v>0.001467315716272601</v>
+        <v>0.04170940170940171</v>
       </c>
       <c r="J16">
-        <v>0.001467315716272601</v>
+        <v>0.04170940170940171</v>
       </c>
       <c r="K16">
-        <v>0.211</v>
+        <v>0.491</v>
       </c>
       <c r="L16">
-        <v>0.001467315716272601</v>
+        <v>0.04196581196581197</v>
       </c>
       <c r="M16">
-        <v>0.186</v>
+        <v>0.022</v>
       </c>
       <c r="N16">
-        <v>0.03795918367346938</v>
+        <v>0.002340425531914893</v>
       </c>
       <c r="O16">
-        <v>0.8815165876777251</v>
+        <v>0.04480651731160896</v>
       </c>
       <c r="P16">
-        <v>0.186</v>
+        <v>0.022</v>
       </c>
       <c r="Q16">
-        <v>0.03795918367346938</v>
+        <v>0.002340425531914893</v>
       </c>
       <c r="R16">
-        <v>0.8815165876777251</v>
+        <v>0.04480651731160896</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2428,67 +2410,73 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>4.92</v>
+        <v>0.111</v>
       </c>
       <c r="V16">
-        <v>1.004081632653061</v>
+        <v>0.01180851063829787</v>
       </c>
       <c r="W16">
-        <v>0.02009523809523809</v>
+        <v>0.1049145299145299</v>
       </c>
       <c r="X16">
-        <v>0.08302001710550982</v>
+        <v>0.136392935094479</v>
       </c>
       <c r="Y16">
-        <v>-0.06292477901027173</v>
+        <v>-0.03147840517994906</v>
       </c>
       <c r="Z16">
-        <v>38.34666666666667</v>
+        <v>2.717138875986995</v>
       </c>
       <c r="AA16">
-        <v>0.05626666666666667</v>
+        <v>0.1133302368787738</v>
       </c>
       <c r="AB16">
-        <v>0.08302001710550982</v>
+        <v>0.1363476245330761</v>
       </c>
       <c r="AC16">
-        <v>-0.02675335043884316</v>
+        <v>-0.02301738765430233</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AG16">
-        <v>-4.92</v>
+        <v>-0.098</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.001381068734728567</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.004774146162320969</v>
       </c>
       <c r="AJ16">
-        <v>246.0000000000052</v>
+        <v>-0.01053536873790583</v>
       </c>
       <c r="AK16">
-        <v>-1.171428571428572</v>
+        <v>-0.03751914241960184</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>0.02653061224489796</v>
+      </c>
+      <c r="AO16">
+        <v>162.6666666666667</v>
       </c>
       <c r="AP16">
-        <v>-22.99065420560748</v>
+        <v>-0.2</v>
+      </c>
+      <c r="AQ16">
+        <v>162.6666666666667</v>
       </c>
     </row>
     <row r="17">
@@ -2499,7 +2487,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Garanti Yatirim Ortakligi A.S. (IBSE:GRNYO)</t>
+          <t>Dagi Yatirim Holding A.S. (IBSE:DAGHL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2508,121 +2496,109 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.0668</v>
-      </c>
-      <c r="E17">
-        <v>0.0164</v>
+        <v>0.8809999999999999</v>
       </c>
       <c r="G17">
-        <v>0.01843137254901961</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>0.01843137254901961</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0.02343137254901961</v>
+        <v>0.02050279329608939</v>
       </c>
       <c r="J17">
-        <v>0.02343137254901961</v>
+        <v>0.01913594040968343</v>
       </c>
       <c r="K17">
-        <v>0.224</v>
+        <v>1.2</v>
       </c>
       <c r="L17">
-        <v>0.02196078431372549</v>
+        <v>0.0670391061452514</v>
       </c>
       <c r="M17">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="N17">
-        <v>0.006424581005586592</v>
+        <v>-0</v>
       </c>
       <c r="O17">
-        <v>0.2053571428571428</v>
+        <v>-0</v>
       </c>
       <c r="P17">
-        <v>0.046</v>
+        <v>-0</v>
       </c>
       <c r="Q17">
-        <v>0.006424581005586592</v>
+        <v>-0</v>
       </c>
       <c r="R17">
-        <v>0.2053571428571428</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
       <c r="U17">
-        <v>0.431</v>
+        <v>0.03</v>
       </c>
       <c r="V17">
-        <v>0.06019553072625698</v>
+        <v>0.00160427807486631</v>
       </c>
       <c r="W17">
-        <v>0.04324324324324325</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="X17">
-        <v>0.08345258034294156</v>
+        <v>0.1420696508774414</v>
       </c>
       <c r="Y17">
-        <v>-0.04020933709969832</v>
+        <v>0.2150732062654158</v>
       </c>
       <c r="Z17">
-        <v>2.266163074872251</v>
+        <v>5.519580635214307</v>
       </c>
       <c r="AA17">
-        <v>0.05309931126416352</v>
+        <v>0.1056223661219036</v>
       </c>
       <c r="AB17">
-        <v>0.08326601422931389</v>
+        <v>0.1395271966252238</v>
       </c>
       <c r="AC17">
-        <v>-0.03016670296515037</v>
+        <v>-0.03390483050332022</v>
       </c>
       <c r="AD17">
-        <v>0.057</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.057</v>
+        <v>1.44</v>
       </c>
       <c r="AG17">
-        <v>-0.374</v>
+        <v>1.41</v>
       </c>
       <c r="AH17">
-        <v>0.007898018567271719</v>
+        <v>0.0714995034756703</v>
       </c>
       <c r="AI17">
-        <v>0.01203293223559215</v>
+        <v>0.6554392353208921</v>
       </c>
       <c r="AJ17">
-        <v>-0.05511346890657235</v>
+        <v>0.07011437095972153</v>
       </c>
       <c r="AK17">
-        <v>-0.08685555039479796</v>
+        <v>0.6506691278264882</v>
       </c>
       <c r="AL17">
-        <v>0.015</v>
+        <v>0.26</v>
       </c>
       <c r="AM17">
-        <v>0.015</v>
-      </c>
-      <c r="AN17">
-        <v>0.2355371900826446</v>
+        <v>0.05300000000000002</v>
       </c>
       <c r="AO17">
-        <v>15.93333333333333</v>
-      </c>
-      <c r="AP17">
-        <v>-1.545454545454545</v>
+        <v>1.411538461538461</v>
       </c>
       <c r="AQ17">
-        <v>15.93333333333333</v>
+        <v>6.92452830188679</v>
       </c>
     </row>
     <row r="18">
@@ -2633,7 +2609,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Gozde Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:GOZDE)</t>
+          <t>Vakif Menkul Kiymet Yatirim Ortakligi A.S. (IBSE:VKFYO)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2642,118 +2618,112 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.887</v>
-      </c>
-      <c r="E18">
-        <v>0.9009999999999999</v>
+        <v>-0.0544</v>
       </c>
       <c r="G18">
-        <v>-0.004059717129387114</v>
+        <v>0.02925925925925926</v>
       </c>
       <c r="H18">
-        <v>-0.004059717129387114</v>
+        <v>0.02925925925925926</v>
       </c>
       <c r="I18">
-        <v>0.1042430591932949</v>
+        <v>0.02876543209876543</v>
       </c>
       <c r="J18">
-        <v>0.1042430591932949</v>
+        <v>0.02876543209876543</v>
       </c>
       <c r="K18">
-        <v>501.5</v>
+        <v>0.234</v>
       </c>
       <c r="L18">
-        <v>2.627029858564693</v>
+        <v>0.02888888888888889</v>
       </c>
       <c r="M18">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="N18">
-        <v>-0</v>
+        <v>0.002307692307692307</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="P18">
-        <v>-0</v>
+        <v>0.03</v>
       </c>
       <c r="Q18">
-        <v>-0</v>
+        <v>0.002307692307692307</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0.1282051282051282</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
       <c r="U18">
-        <v>0.006</v>
+        <v>0.044</v>
       </c>
       <c r="V18">
-        <v>2.273588480485032e-05</v>
+        <v>0.003384615384615384</v>
       </c>
       <c r="W18">
-        <v>1.808510638297872</v>
+        <v>0.06628895184135979</v>
       </c>
       <c r="X18">
-        <v>0.107892281042897</v>
+        <v>0.1363006682644232</v>
       </c>
       <c r="Y18">
-        <v>1.700618357254975</v>
+        <v>-0.07001171642306338</v>
       </c>
       <c r="Z18">
-        <v>0.3573895771046016</v>
+        <v>3.095147115017196</v>
       </c>
       <c r="AA18">
-        <v>0.03725538284118161</v>
+        <v>0.08903324417271687</v>
       </c>
       <c r="AB18">
-        <v>0.09280041733048622</v>
+        <v>0.1362956357978713</v>
       </c>
       <c r="AC18">
-        <v>-0.0555450344893046</v>
+        <v>-0.04726239162515446</v>
       </c>
       <c r="AD18">
-        <v>120.8</v>
+        <v>0.002</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>120.8</v>
+        <v>0.002</v>
       </c>
       <c r="AG18">
-        <v>120.794</v>
+        <v>-0.042</v>
       </c>
       <c r="AH18">
-        <v>0.3140109175981284</v>
+        <v>0.0001538224888478696</v>
       </c>
       <c r="AI18">
-        <v>0.1399606071138918</v>
+        <v>0.001040582726326743</v>
       </c>
       <c r="AJ18">
-        <v>0.3140002183553682</v>
+        <v>-0.00324124093224263</v>
       </c>
       <c r="AK18">
-        <v>0.1399546283487083</v>
+        <v>-0.02236421725239617</v>
       </c>
       <c r="AL18">
-        <v>28.2</v>
+        <v>0</v>
       </c>
       <c r="AM18">
-        <v>28.107</v>
+        <v>0</v>
       </c>
       <c r="AN18">
-        <v>6.07035175879397</v>
-      </c>
-      <c r="AO18">
-        <v>0.7056737588652482</v>
+        <v>0.008547008547008546</v>
       </c>
       <c r="AP18">
-        <v>6.070050251256282</v>
-      </c>
-      <c r="AQ18">
-        <v>0.7080086811114669</v>
+        <v>-0.1794871794871795</v>
       </c>
     </row>
     <row r="19">
@@ -2764,7 +2734,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Marka Yatirim Holding A.S. (IBSE:MARKA)</t>
+          <t>Is Girisim Sermayesi Yatirim Ortakligi AS (IBSE:ISGSY)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2773,28 +2743,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>3.707</v>
-      </c>
-      <c r="E19">
-        <v>0.444</v>
+        <v>0.185</v>
       </c>
       <c r="G19">
-        <v>0.06163793103448276</v>
+        <v>0.6642335766423357</v>
       </c>
       <c r="H19">
-        <v>0.06163793103448276</v>
+        <v>0.6642335766423357</v>
       </c>
       <c r="I19">
-        <v>0.02413793103448276</v>
+        <v>0.4861313868613139</v>
       </c>
       <c r="J19">
-        <v>0.02413793103448276</v>
+        <v>0.4861313868613139</v>
       </c>
       <c r="K19">
-        <v>0.065</v>
+        <v>0.666</v>
       </c>
       <c r="L19">
-        <v>0.02801724137931035</v>
+        <v>0.4861313868613139</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2818,73 +2785,67 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.192</v>
+        <v>2.35</v>
       </c>
       <c r="V19">
-        <v>0.02869955156950673</v>
+        <v>0.03415697674418605</v>
       </c>
       <c r="W19">
-        <v>0.0196969696969697</v>
+        <v>0.02242424242424243</v>
       </c>
       <c r="X19">
-        <v>0.08389719042059443</v>
+        <v>0.1363742241539245</v>
       </c>
       <c r="Y19">
-        <v>-0.06420022072362473</v>
+        <v>-0.113949981729682</v>
       </c>
       <c r="Z19">
-        <v>0.6709080393290919</v>
+        <v>0.05837736492244759</v>
       </c>
       <c r="AA19">
-        <v>0.01619433198380567</v>
+        <v>0.02837906937105847</v>
       </c>
       <c r="AB19">
-        <v>0.08351484534237344</v>
+        <v>0.1363370919718991</v>
       </c>
       <c r="AC19">
-        <v>-0.06732051335856777</v>
+        <v>-0.1079580226008406</v>
       </c>
       <c r="AD19">
-        <v>0.108</v>
+        <v>0.078</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0.108</v>
+        <v>0.078</v>
       </c>
       <c r="AG19">
-        <v>-0.08400000000000001</v>
+        <v>-2.272</v>
       </c>
       <c r="AH19">
-        <v>0.01588702559576346</v>
+        <v>0.001132437062632481</v>
       </c>
       <c r="AI19">
-        <v>0.05781584582441113</v>
+        <v>0.005207637868874349</v>
       </c>
       <c r="AJ19">
-        <v>-0.01271571298819255</v>
+        <v>-0.03415103415103416</v>
       </c>
       <c r="AK19">
-        <v>-0.05011933174224344</v>
+        <v>-0.1799176433322775</v>
       </c>
       <c r="AL19">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AM19">
-        <v>0.001000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AN19">
-        <v>1.542857142857143</v>
-      </c>
-      <c r="AO19">
-        <v>2.8</v>
+        <v>0.115727002967359</v>
       </c>
       <c r="AP19">
-        <v>-1.2</v>
-      </c>
-      <c r="AQ19">
-        <v>55.99999999999995</v>
+        <v>-3.370919881305638</v>
       </c>
     </row>
     <row r="20">
@@ -2895,7 +2856,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Yesil Yatirim Holding Anonim Sirketi (IBSE:YESIL)</t>
+          <t>Osmanli Yatirim Menkul Degerler A.S. (IBSE:OSMEN)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2903,92 +2864,113 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D20">
+        <v>0.42</v>
+      </c>
       <c r="E20">
-        <v>1.066</v>
+        <v>1.13</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>5.23</v>
+        <v>8.02</v>
+      </c>
+      <c r="L20">
+        <v>0.06098859315589353</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>0.297</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.004194915254237288</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0.03703241895261845</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>0.297</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.004194915254237288</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.03703241895261845</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>0.915</v>
+        <v>22.8</v>
       </c>
       <c r="V20">
-        <v>0.03101694915254237</v>
+        <v>0.3220338983050848</v>
       </c>
       <c r="W20">
-        <v>0.1644654088050315</v>
+        <v>0.4717647058823529</v>
       </c>
       <c r="X20">
-        <v>0.08302001710550982</v>
+        <v>0.1521930649041999</v>
       </c>
       <c r="Y20">
-        <v>0.08144539169952164</v>
+        <v>0.319571640978153</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>12.28971962616822</v>
       </c>
       <c r="AA20">
-        <v>-0.001013781811281124</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.08302001710550982</v>
+        <v>0.1436950820907051</v>
       </c>
       <c r="AC20">
-        <v>-0.08403379891679094</v>
+        <v>-0.1436950820907051</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG20">
-        <v>-0.915</v>
+        <v>-7.800000000000001</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>0.1748251748251748</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>0.4901960784313725</v>
       </c>
       <c r="AJ20">
-        <v>-0.03200979534721007</v>
+        <v>-0.1238095238095238</v>
       </c>
       <c r="AK20">
-        <v>-0.01652071860612079</v>
+        <v>-1</v>
       </c>
       <c r="AL20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-0.245</v>
+        <v>-1.99</v>
       </c>
       <c r="AQ20">
-        <v>0.163265306122449</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="21">
@@ -2999,7 +2981,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Osmanli Yatirim Menkul Degerler A.S. (IBSE:OSMEN)</t>
+          <t>ÜNLÜ Yatirim Holding A.S. (IBSE:UNLU)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3007,12 +2989,6 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D21">
-        <v>0.66</v>
-      </c>
-      <c r="E21">
-        <v>0.968</v>
-      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -3026,91 +3002,91 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>7.87</v>
+        <v>11.4</v>
       </c>
       <c r="L21">
-        <v>0.01867584242999526</v>
+        <v>0.02406078514140988</v>
       </c>
       <c r="M21">
-        <v>0.383</v>
+        <v>1.454</v>
       </c>
       <c r="N21">
-        <v>0.009598997493734336</v>
+        <v>0.01511434511434511</v>
       </c>
       <c r="O21">
-        <v>0.04866581956797967</v>
+        <v>0.1275438596491228</v>
       </c>
       <c r="P21">
-        <v>0.383</v>
+        <v>0.945</v>
       </c>
       <c r="Q21">
-        <v>0.009598997493734336</v>
+        <v>0.009823284823284822</v>
       </c>
       <c r="R21">
-        <v>0.04866581956797967</v>
+        <v>0.08289473684210526</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>0.509</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>0.3500687757909216</v>
       </c>
       <c r="U21">
-        <v>17.3</v>
+        <v>11.6</v>
       </c>
       <c r="V21">
-        <v>0.4335839598997494</v>
+        <v>0.1205821205821206</v>
       </c>
       <c r="W21">
-        <v>0.7567307692307692</v>
+        <v>0.1890547263681592</v>
       </c>
       <c r="X21">
-        <v>0.09799987050221373</v>
+        <v>0.1559531411314349</v>
       </c>
       <c r="Y21">
-        <v>0.6587308987285555</v>
+        <v>0.0331015852367243</v>
       </c>
       <c r="Z21">
-        <v>-82.78978388998036</v>
+        <v>9.074889867841408</v>
       </c>
       <c r="AA21">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.08975112856155801</v>
+        <v>0.145689945451083</v>
       </c>
       <c r="AC21">
-        <v>-0.08975112856155801</v>
+        <v>-0.145689945451083</v>
       </c>
       <c r="AD21">
-        <v>11</v>
+        <v>25.2</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>11</v>
+        <v>25.2</v>
       </c>
       <c r="AG21">
-        <v>-6.300000000000001</v>
+        <v>13.6</v>
       </c>
       <c r="AH21">
-        <v>0.2161100196463654</v>
+        <v>0.2075782537067545</v>
       </c>
       <c r="AI21">
-        <v>0.3928571428571428</v>
+        <v>0.3766816143497758</v>
       </c>
       <c r="AJ21">
-        <v>-0.1875000000000001</v>
+        <v>0.1238615664845173</v>
       </c>
       <c r="AK21">
-        <v>-0.588785046728972</v>
+        <v>0.2459312839059674</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1.94</v>
+        <v>-17.9</v>
       </c>
       <c r="AQ21">
         <v>-0</v>
@@ -3124,7 +3100,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Is Girisim Sermayesi Yatirim Ortakligi AS (IBSE:ISGSY)</t>
+          <t>Verusaturk Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:VERTU)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3132,110 +3108,104 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D22">
-        <v>-0.06849999999999999</v>
-      </c>
-      <c r="G22">
-        <v>0.3122923588039866</v>
-      </c>
-      <c r="H22">
-        <v>0.3122923588039866</v>
-      </c>
-      <c r="I22">
-        <v>-0.3333333333333333</v>
-      </c>
-      <c r="J22">
-        <v>-0.3333333333333333</v>
+      <c r="E22">
+        <v>1.811</v>
       </c>
       <c r="K22">
-        <v>-0.302</v>
-      </c>
-      <c r="L22">
-        <v>-0.3344407530454042</v>
+        <v>51.6</v>
       </c>
       <c r="M22">
-        <v>-0</v>
+        <v>0.281</v>
       </c>
       <c r="N22">
-        <v>-0</v>
+        <v>0.002345575959933222</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>0.005445736434108527</v>
       </c>
       <c r="P22">
-        <v>-0</v>
+        <v>0.281</v>
       </c>
       <c r="Q22">
-        <v>-0</v>
+        <v>0.002345575959933222</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>0.005445736434108527</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
       <c r="U22">
-        <v>6.32</v>
+        <v>0.004</v>
       </c>
       <c r="V22">
-        <v>0.1341825902335456</v>
+        <v>3.33889816360601e-05</v>
       </c>
       <c r="W22">
-        <v>-0.008728323699421964</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="X22">
-        <v>0.08312153662152315</v>
+        <v>0.1378932143151368</v>
       </c>
       <c r="Y22">
-        <v>-0.09184986032094511</v>
+        <v>0.3236452472233248</v>
       </c>
       <c r="Z22">
-        <v>0.02973426849748098</v>
+        <v>0</v>
       </c>
       <c r="AA22">
-        <v>-0.00991142283249366</v>
+        <v>-0.01106659689277411</v>
       </c>
       <c r="AB22">
-        <v>0.08307810196998602</v>
+        <v>0.1371754140174368</v>
       </c>
       <c r="AC22">
-        <v>-0.09298952480247968</v>
+        <v>-0.1482420109102109</v>
       </c>
       <c r="AD22">
-        <v>0.08799999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0.08799999999999999</v>
+        <v>2.56</v>
       </c>
       <c r="AG22">
-        <v>-6.232</v>
+        <v>2.556</v>
       </c>
       <c r="AH22">
-        <v>0.001864880901924218</v>
+        <v>0.02092186989212161</v>
       </c>
       <c r="AI22">
-        <v>0.002954209748892171</v>
+        <v>0.02382281779266704</v>
       </c>
       <c r="AJ22">
-        <v>-0.1524909464617794</v>
+        <v>0.0208898623688254</v>
       </c>
       <c r="AK22">
-        <v>-0.2655530935742287</v>
+        <v>0.02378648004764741</v>
       </c>
       <c r="AL22">
-        <v>0</v>
+        <v>0.631</v>
       </c>
       <c r="AM22">
-        <v>0</v>
+        <v>0.611</v>
       </c>
       <c r="AN22">
-        <v>-0.2983050847457627</v>
+        <v>-2</v>
+      </c>
+      <c r="AO22">
+        <v>-2.044374009508716</v>
       </c>
       <c r="AP22">
-        <v>21.12542372881356</v>
+        <v>-1.996875</v>
+      </c>
+      <c r="AQ22">
+        <v>-2.111292962356792</v>
       </c>
     </row>
     <row r="23">
@@ -3255,10 +3225,10 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.9129999999999999</v>
+        <v>0.256</v>
       </c>
       <c r="E23">
-        <v>0.907</v>
+        <v>2.076</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3273,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="K23">
-        <v>9.52</v>
+        <v>19.7</v>
       </c>
       <c r="L23">
-        <v>0.005905340859748155</v>
+        <v>0.03512212515599929</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3300,61 +3270,61 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>45</v>
+        <v>37.2</v>
       </c>
       <c r="V23">
-        <v>0.7718696397941681</v>
+        <v>0.2563749138525155</v>
       </c>
       <c r="W23">
-        <v>0.8576576576576577</v>
+        <v>0.7975708502024291</v>
       </c>
       <c r="X23">
-        <v>0.11936829384122</v>
+        <v>0.1658811993714438</v>
       </c>
       <c r="Y23">
-        <v>0.7382893638164376</v>
+        <v>0.6316896508309854</v>
       </c>
       <c r="Z23">
-        <v>-1151.500000000001</v>
+        <v>29.99465240641711</v>
       </c>
       <c r="AA23">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB23">
-        <v>0.09648125640595183</v>
+        <v>0.1482669368881177</v>
       </c>
       <c r="AC23">
-        <v>-0.09648125640595183</v>
+        <v>-0.1482669368881177</v>
       </c>
       <c r="AD23">
-        <v>39</v>
+        <v>57.2</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>39</v>
+        <v>57.2</v>
       </c>
       <c r="AG23">
-        <v>-6</v>
+        <v>20</v>
       </c>
       <c r="AH23">
-        <v>0.4008221993833505</v>
+        <v>0.2827483934750371</v>
       </c>
       <c r="AI23">
-        <v>0.6122448979591837</v>
+        <v>0.6434195725534309</v>
       </c>
       <c r="AJ23">
-        <v>-0.1147227533460803</v>
+        <v>0.1211387038158692</v>
       </c>
       <c r="AK23">
-        <v>-0.320855614973262</v>
+        <v>0.3868471953578336</v>
       </c>
       <c r="AL23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>-1.14</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AQ23">
         <v>-0</v>
@@ -3368,7 +3338,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Dagi Yatirim Holding A.S. (IBSE:DAGHL)</t>
+          <t>Hedef Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HDFGS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3376,38 +3346,17 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D24">
-        <v>-0.195</v>
-      </c>
-      <c r="E24">
-        <v>0.466</v>
-      </c>
-      <c r="G24">
-        <v>-0.05285412262156449</v>
-      </c>
-      <c r="H24">
-        <v>-0.05285412262156449</v>
-      </c>
-      <c r="I24">
-        <v>-0.1183932346723044</v>
-      </c>
-      <c r="J24">
-        <v>-0.08467157541736532</v>
-      </c>
       <c r="K24">
-        <v>1.04</v>
-      </c>
-      <c r="L24">
-        <v>2.198731501057082</v>
+        <v>-1.1</v>
       </c>
       <c r="M24">
-        <v>-0</v>
+        <v>2.14</v>
       </c>
       <c r="N24">
-        <v>-0</v>
+        <v>0.03375394321766562</v>
       </c>
       <c r="O24">
-        <v>-0</v>
+        <v>-1.945454545454545</v>
       </c>
       <c r="P24">
         <v>-0</v>
@@ -3416,73 +3365,82 @@
         <v>-0</v>
       </c>
       <c r="R24">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>2.14</v>
+      </c>
+      <c r="T24">
+        <v>1</v>
       </c>
       <c r="U24">
-        <v>0.117</v>
+        <v>0.011</v>
       </c>
       <c r="V24">
-        <v>0.01325028312570782</v>
+        <v>0.0001735015772870662</v>
       </c>
       <c r="W24">
-        <v>0.3895131086142322</v>
+        <v>-0.01361386138613862</v>
       </c>
       <c r="X24">
-        <v>0.08302001710550982</v>
+        <v>0.1363376642142887</v>
       </c>
       <c r="Y24">
-        <v>0.3064930915087224</v>
+        <v>-0.1499515256004273</v>
       </c>
       <c r="Z24">
-        <v>0.177352830896138</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>-0.01501674359670559</v>
+        <v>-0.01195922019331342</v>
       </c>
       <c r="AB24">
-        <v>0.08302001710550982</v>
+        <v>0.1363164969013344</v>
       </c>
       <c r="AC24">
-        <v>-0.09803676070221541</v>
+        <v>-0.1482757170946478</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="AG24">
-        <v>-0.117</v>
+        <v>0.03</v>
       </c>
       <c r="AH24">
-        <v>0</v>
+        <v>0.0006462697624564557</v>
       </c>
       <c r="AI24">
-        <v>0</v>
+        <v>0.001153597253875805</v>
       </c>
       <c r="AJ24">
-        <v>-0.01342821071961437</v>
+        <v>0.0004729623206684534</v>
       </c>
       <c r="AK24">
-        <v>-0.0360777058279371</v>
+        <v>0.0008443568815085843</v>
       </c>
       <c r="AL24">
-        <v>0.007</v>
+        <v>0.199</v>
       </c>
       <c r="AM24">
-        <v>-0.001</v>
+        <v>0.199</v>
+      </c>
+      <c r="AN24">
+        <v>-0.04371002132196163</v>
       </c>
       <c r="AO24">
-        <v>-8</v>
+        <v>-4.768844221105527</v>
+      </c>
+      <c r="AP24">
+        <v>-0.03198294243070363</v>
       </c>
       <c r="AQ24">
-        <v>56</v>
+        <v>-4.768844221105527</v>
       </c>
     </row>
     <row r="25">
@@ -3493,7 +3451,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hub Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HUBVC)</t>
+          <t>Verusa Holding A.S. (IBSE:VERUS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3502,118 +3460,121 @@
         </is>
       </c>
       <c r="D25">
-        <v>-0.0418</v>
+        <v>0.327</v>
       </c>
       <c r="E25">
-        <v>0.883</v>
+        <v>0.797</v>
       </c>
       <c r="G25">
-        <v>-0.5195530726256984</v>
+        <v>-0.2368983957219251</v>
       </c>
       <c r="H25">
-        <v>-0.5195530726256984</v>
+        <v>-0.2368983957219251</v>
       </c>
       <c r="I25">
-        <v>-0.6871508379888268</v>
+        <v>-0.05828877005347594</v>
       </c>
       <c r="J25">
-        <v>-0.6871508379888268</v>
+        <v>-0.05363336333633364</v>
       </c>
       <c r="K25">
-        <v>2.89</v>
+        <v>19.8</v>
       </c>
       <c r="L25">
-        <v>8.072625698324023</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="M25">
-        <v>-0</v>
+        <v>4.429</v>
       </c>
       <c r="N25">
-        <v>-0</v>
+        <v>0.01081298828125</v>
       </c>
       <c r="O25">
-        <v>-0</v>
+        <v>0.2236868686868687</v>
       </c>
       <c r="P25">
-        <v>-0</v>
+        <v>0.129</v>
       </c>
       <c r="Q25">
-        <v>-0</v>
+        <v>0.00031494140625</v>
       </c>
       <c r="R25">
-        <v>-0</v>
+        <v>0.006515151515151515</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>4.300000000000001</v>
+      </c>
+      <c r="T25">
+        <v>0.9708737864077671</v>
       </c>
       <c r="U25">
-        <v>0.274</v>
+        <v>4.74</v>
       </c>
       <c r="V25">
-        <v>0.01323671497584541</v>
+        <v>0.011572265625</v>
       </c>
       <c r="W25">
-        <v>0.3905405405405405</v>
+        <v>0.2780898876404495</v>
       </c>
       <c r="X25">
-        <v>0.08303839160289102</v>
+        <v>0.13819510800398</v>
       </c>
       <c r="Y25">
-        <v>0.3075021489376495</v>
+        <v>0.1398947796364694</v>
       </c>
       <c r="Z25">
-        <v>0.05137772675086107</v>
+        <v>0.2331089503864373</v>
       </c>
       <c r="AA25">
-        <v>-0.03530424799081515</v>
+        <v>-0.01250241703302716</v>
       </c>
       <c r="AB25">
-        <v>0.0830313701969177</v>
+        <v>0.1373380859805351</v>
       </c>
       <c r="AC25">
-        <v>-0.1183356181877328</v>
+        <v>-0.1498405030135622</v>
       </c>
       <c r="AD25">
-        <v>0.007</v>
+        <v>10.4</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>0.007</v>
+        <v>10.4</v>
       </c>
       <c r="AG25">
-        <v>-0.267</v>
+        <v>5.66</v>
       </c>
       <c r="AH25">
-        <v>0.0003380499348046554</v>
+        <v>0.02476190476190476</v>
       </c>
       <c r="AI25">
-        <v>0.0007159660427534009</v>
+        <v>0.1125541125541125</v>
       </c>
       <c r="AJ25">
-        <v>-0.01306709734253414</v>
+        <v>0.01363001493040505</v>
       </c>
       <c r="AK25">
-        <v>-0.02809639061349048</v>
+        <v>0.0645676477298654</v>
       </c>
       <c r="AL25">
-        <v>0.001</v>
+        <v>0.994</v>
       </c>
       <c r="AM25">
-        <v>-0.035</v>
+        <v>-0.226</v>
       </c>
       <c r="AN25">
-        <v>-0.02788844621513944</v>
+        <v>-13.90374331550802</v>
       </c>
       <c r="AO25">
-        <v>-246</v>
+        <v>-1.096579476861167</v>
       </c>
       <c r="AP25">
-        <v>1.063745019920319</v>
+        <v>-7.566844919786097</v>
       </c>
       <c r="AQ25">
-        <v>7.028571428571429</v>
+        <v>4.823008849557523</v>
       </c>
     </row>
     <row r="26">
@@ -3624,7 +3585,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Atlantis Yatirim Holding A.S. (IBSE:ATSYH)</t>
+          <t>Denge Yatirim Holding A.S. (IBSE:DENGE)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3633,22 +3594,22 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.04231738035264484</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="H26">
-        <v>0.04231738035264484</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="I26">
-        <v>0.08589420654911839</v>
+        <v>-0.0495</v>
       </c>
       <c r="J26">
-        <v>0.06383394585071094</v>
+        <v>-0.04244290540540541</v>
       </c>
       <c r="K26">
-        <v>0.193</v>
+        <v>13.1</v>
       </c>
       <c r="L26">
-        <v>0.04861460957178841</v>
+        <v>0.655</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3672,73 +3633,439 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>0.008999999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="V26">
-        <v>0.001688555347091932</v>
+        <v>0.1893223819301848</v>
       </c>
       <c r="W26">
-        <v>0.636963696369637</v>
+        <v>0.2176079734219269</v>
       </c>
       <c r="X26">
-        <v>0.08303021147955943</v>
+        <v>0.1695835556192742</v>
       </c>
       <c r="Y26">
-        <v>0.5539334848900775</v>
+        <v>0.04802441780265268</v>
       </c>
       <c r="Z26">
-        <v>-10.75880758807588</v>
+        <v>0.2531645569620253</v>
       </c>
       <c r="AA26">
-        <v>-0.6867771409954536</v>
+        <v>-0.01074503934314061</v>
       </c>
       <c r="AB26">
-        <v>0.08302585966571706</v>
+        <v>0.1502040994027945</v>
       </c>
       <c r="AC26">
-        <v>-0.7698030006611707</v>
+        <v>-0.1609491387459351</v>
       </c>
       <c r="AD26">
+        <v>21.6</v>
+      </c>
+      <c r="AE26">
+        <v>0</v>
+      </c>
+      <c r="AF26">
+        <v>21.6</v>
+      </c>
+      <c r="AG26">
+        <v>12.38</v>
+      </c>
+      <c r="AH26">
+        <v>0.3072546230440967</v>
+      </c>
+      <c r="AI26">
+        <v>0.3</v>
+      </c>
+      <c r="AJ26">
+        <v>0.2026850032743942</v>
+      </c>
+      <c r="AK26">
+        <v>0.1971965594138261</v>
+      </c>
+      <c r="AL26">
+        <v>2.78</v>
+      </c>
+      <c r="AM26">
+        <v>-32.62</v>
+      </c>
+      <c r="AN26">
+        <v>-26.63378545006165</v>
+      </c>
+      <c r="AO26">
+        <v>-0.3561151079136691</v>
+      </c>
+      <c r="AP26">
+        <v>-15.26510480887793</v>
+      </c>
+      <c r="AQ26">
+        <v>0.03034947884733293</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gozde Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:GOZDE)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>-0.46</v>
+      </c>
+      <c r="E27">
+        <v>1.38</v>
+      </c>
+      <c r="G27">
+        <v>-139.2</v>
+      </c>
+      <c r="H27">
+        <v>-139.2</v>
+      </c>
+      <c r="I27">
+        <v>-636</v>
+      </c>
+      <c r="J27">
+        <v>-636</v>
+      </c>
+      <c r="K27">
+        <v>316.8</v>
+      </c>
+      <c r="L27">
+        <v>12672</v>
+      </c>
+      <c r="M27">
+        <v>-0</v>
+      </c>
+      <c r="N27">
+        <v>-0</v>
+      </c>
+      <c r="O27">
+        <v>-0</v>
+      </c>
+      <c r="P27">
+        <v>-0</v>
+      </c>
+      <c r="Q27">
+        <v>-0</v>
+      </c>
+      <c r="R27">
+        <v>-0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.4267816246800485</v>
+      </c>
+      <c r="X27">
+        <v>0.1512435953330112</v>
+      </c>
+      <c r="Y27">
+        <v>0.2755380293470373</v>
+      </c>
+      <c r="Z27">
+        <v>2.896555879197399e-05</v>
+      </c>
+      <c r="AA27">
+        <v>-0.01842209539169546</v>
+      </c>
+      <c r="AB27">
+        <v>0.1433263930270297</v>
+      </c>
+      <c r="AC27">
+        <v>-0.1617484884187252</v>
+      </c>
+      <c r="AD27">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="AG27">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="AH27">
+        <v>0.1661218996346857</v>
+      </c>
+      <c r="AI27">
+        <v>0.1138189961796865</v>
+      </c>
+      <c r="AJ27">
+        <v>0.1661218996346857</v>
+      </c>
+      <c r="AK27">
+        <v>0.1138189961796865</v>
+      </c>
+      <c r="AL27">
+        <v>18.5</v>
+      </c>
+      <c r="AM27">
+        <v>18.5</v>
+      </c>
+      <c r="AN27">
+        <v>-5.433962264150944</v>
+      </c>
+      <c r="AO27">
+        <v>-0.8594594594594595</v>
+      </c>
+      <c r="AP27">
+        <v>-5.433962264150944</v>
+      </c>
+      <c r="AQ27">
+        <v>-0.8594594594594595</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Yesil Yatirim Holding Anonim Sirketi (IBSE:YESIL)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K28">
+        <v>-0.574</v>
+      </c>
+      <c r="M28">
+        <v>-0</v>
+      </c>
+      <c r="N28">
+        <v>-0</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>-0</v>
+      </c>
+      <c r="Q28">
+        <v>-0</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="U28">
         <v>0.001</v>
       </c>
-      <c r="AE26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>0.001</v>
-      </c>
-      <c r="AG26">
+      <c r="V28">
+        <v>1.6e-05</v>
+      </c>
+      <c r="W28">
+        <v>-0.01019538188277087</v>
+      </c>
+      <c r="X28">
+        <v>0.1362891195533376</v>
+      </c>
+      <c r="Y28">
+        <v>-0.1464845014361085</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>-0.02834702536787939</v>
+      </c>
+      <c r="AB28">
+        <v>0.1362891195533376</v>
+      </c>
+      <c r="AC28">
+        <v>-0.164636144921217</v>
+      </c>
+      <c r="AD28">
+        <v>0</v>
+      </c>
+      <c r="AE28">
+        <v>0</v>
+      </c>
+      <c r="AF28">
+        <v>0</v>
+      </c>
+      <c r="AG28">
+        <v>-0.001</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>0</v>
+      </c>
+      <c r="AJ28">
+        <v>-1.600025600409606e-05</v>
+      </c>
+      <c r="AK28">
+        <v>-3.788022273570969e-05</v>
+      </c>
+      <c r="AL28">
+        <v>0.002</v>
+      </c>
+      <c r="AM28">
+        <v>-0.047</v>
+      </c>
+      <c r="AO28">
+        <v>-785</v>
+      </c>
+      <c r="AQ28">
+        <v>33.40425531914894</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Turkey</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hub Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HUBVC)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>-0.58</v>
+      </c>
+      <c r="E29">
+        <v>1.628</v>
+      </c>
+      <c r="G29">
+        <v>-205.5</v>
+      </c>
+      <c r="H29">
+        <v>-205.5</v>
+      </c>
+      <c r="I29">
+        <v>-235.5</v>
+      </c>
+      <c r="J29">
+        <v>-235.5</v>
+      </c>
+      <c r="K29">
+        <v>5.62</v>
+      </c>
+      <c r="L29">
+        <v>2810</v>
+      </c>
+      <c r="M29">
+        <v>-0</v>
+      </c>
+      <c r="N29">
+        <v>-0</v>
+      </c>
+      <c r="O29">
+        <v>-0</v>
+      </c>
+      <c r="P29">
+        <v>-0</v>
+      </c>
+      <c r="Q29">
+        <v>-0</v>
+      </c>
+      <c r="R29">
+        <v>-0</v>
+      </c>
+      <c r="S29">
+        <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0.053</v>
+      </c>
+      <c r="V29">
+        <v>0.004690265486725663</v>
+      </c>
+      <c r="W29">
+        <v>0.5752302968270215</v>
+      </c>
+      <c r="X29">
+        <v>0.1363156918089327</v>
+      </c>
+      <c r="Y29">
+        <v>0.4389146050180888</v>
+      </c>
+      <c r="Z29">
+        <v>0.0002104598547827002</v>
+      </c>
+      <c r="AA29">
+        <v>-0.04956329580132589</v>
+      </c>
+      <c r="AB29">
+        <v>0.1363051450684522</v>
+      </c>
+      <c r="AC29">
+        <v>-0.1858684408697781</v>
+      </c>
+      <c r="AD29">
+        <v>0.004</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0.004</v>
+      </c>
+      <c r="AG29">
+        <v>-0.049</v>
+      </c>
+      <c r="AH29">
+        <v>0.0003538570417551309</v>
+      </c>
+      <c r="AI29">
+        <v>0.0003635041802980735</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.004355168429472935</v>
+      </c>
+      <c r="AK29">
+        <v>-0.004474477216692539</v>
+      </c>
+      <c r="AL29">
+        <v>0.003</v>
+      </c>
+      <c r="AM29">
         <v>-0.008</v>
       </c>
-      <c r="AH26">
-        <v>0.00018758206715438</v>
-      </c>
-      <c r="AI26">
-        <v>0.001564945226917058</v>
-      </c>
-      <c r="AJ26">
-        <v>-0.001503194287861706</v>
-      </c>
-      <c r="AK26">
-        <v>-0.0126984126984127</v>
-      </c>
-      <c r="AL26">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="AM26">
-        <v>-0.02700000000000001</v>
-      </c>
-      <c r="AN26">
-        <v>0.002824858757062147</v>
-      </c>
-      <c r="AO26">
-        <v>3.875</v>
-      </c>
-      <c r="AP26">
-        <v>-0.02259887005649718</v>
-      </c>
-      <c r="AQ26">
-        <v>-12.62962962962963</v>
+      <c r="AN29">
+        <v>-0.008438818565400845</v>
+      </c>
+      <c r="AO29">
+        <v>-157</v>
+      </c>
+      <c r="AP29">
+        <v>0.1033755274261604</v>
+      </c>
+      <c r="AQ29">
+        <v>58.87499999999999</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/turkey/turkey_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/turkey/turkey_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.193</v>
+        <v>0.4195</v>
       </c>
       <c r="E2">
-        <v>0.724</v>
+        <v>0.8095000000000001</v>
       </c>
       <c r="G2">
-        <v>0.03109819861087577</v>
+        <v>0.1001337683912324</v>
       </c>
       <c r="H2">
-        <v>0.03069169754066853</v>
+        <v>0.1000265538518649</v>
       </c>
       <c r="I2">
-        <v>0.05364774038709477</v>
+        <v>0.1521554925931662</v>
       </c>
       <c r="J2">
-        <v>0.04966112552953437</v>
+        <v>0.1396225057518206</v>
       </c>
       <c r="K2">
-        <v>546.278</v>
+        <v>838.732</v>
       </c>
       <c r="L2">
-        <v>0.2367405028045541</v>
+        <v>0.3223091936659648</v>
       </c>
       <c r="M2">
-        <v>11.248</v>
+        <v>21.81</v>
       </c>
       <c r="N2">
-        <v>0.004747594124599022</v>
+        <v>0.009295169580374876</v>
       </c>
       <c r="O2">
-        <v>0.02059024892087911</v>
+        <v>0.02600353867504758</v>
       </c>
       <c r="P2">
-        <v>4.298999999999999</v>
+        <v>13.35</v>
       </c>
       <c r="Q2">
-        <v>0.001814536552422759</v>
+        <v>0.005689615492801677</v>
       </c>
       <c r="R2">
-        <v>0.007869619497764872</v>
+        <v>0.0159168840583166</v>
       </c>
       <c r="S2">
-        <v>6.949000000000001</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="T2">
-        <v>0.617798719772404</v>
+        <v>0.3878954607977992</v>
       </c>
       <c r="U2">
-        <v>137.546</v>
+        <v>255.063</v>
       </c>
       <c r="V2">
-        <v>0.05805588384264731</v>
+        <v>0.1087048986097733</v>
       </c>
       <c r="W2">
-        <v>0.2642857142857143</v>
+        <v>0.434640522875817</v>
       </c>
       <c r="X2">
-        <v>0.1363742241539245</v>
+        <v>0.1109883907097797</v>
       </c>
       <c r="Y2">
-        <v>0.1279114901317898</v>
+        <v>0.3236521321660373</v>
       </c>
       <c r="Z2">
-        <v>1.487363357378266</v>
+        <v>1.864799711636926</v>
       </c>
       <c r="AA2">
-        <v>0.1133302368787738</v>
+        <v>0.2577680525164113</v>
       </c>
       <c r="AB2">
-        <v>0.1363370919718991</v>
+        <v>0.1109521396568795</v>
       </c>
       <c r="AC2">
-        <v>-0.02301738765430233</v>
+        <v>0.1468687148247907</v>
       </c>
       <c r="AD2">
-        <v>277.497</v>
+        <v>274.964</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>277.497</v>
+        <v>274.964</v>
       </c>
       <c r="AG2">
-        <v>139.951</v>
+        <v>19.90100000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1048465313558749</v>
+        <v>0.1048942832379115</v>
       </c>
       <c r="AI2">
-        <v>0.1685164200531242</v>
+        <v>0.1339624709811478</v>
       </c>
       <c r="AJ2">
-        <v>0.0557762366633176</v>
+        <v>0.008410243753806083</v>
       </c>
       <c r="AK2">
-        <v>0.09273436878793502</v>
+        <v>0.0110715990480016</v>
       </c>
       <c r="AL2">
-        <v>33.568</v>
+        <v>45.161</v>
       </c>
       <c r="AM2">
-        <v>-41.44</v>
+        <v>-101.772</v>
       </c>
       <c r="AN2">
-        <v>2.200750245852235</v>
+        <v>2.049202197032367</v>
       </c>
       <c r="AO2">
-        <v>3.687797902764538</v>
+        <v>8.767476362348043</v>
       </c>
       <c r="AP2">
-        <v>1.109911810424135</v>
+        <v>0.1483145899941125</v>
       </c>
       <c r="AQ2">
-        <v>-2.987258687258687</v>
+        <v>-3.89053963762135</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hedef Holding A.S (IBSE:HEDEF)</t>
+          <t>1000 Yatirimlar Holding Anonim Sirketi (IBSE:BINHO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1442786069651741</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.1442786069651741</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9875621890547264</v>
+        <v>0.9954870251974427</v>
       </c>
       <c r="J3">
-        <v>0.805411829740188</v>
+        <v>0.7489832209085422</v>
       </c>
       <c r="K3">
-        <v>33.1</v>
+        <v>316.4</v>
       </c>
       <c r="L3">
-        <v>0.8233830845771144</v>
+        <v>1.189921022940955</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,58 +761,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.068</v>
+        <v>0.013</v>
       </c>
       <c r="V3">
-        <v>0.0001846320934021179</v>
+        <v>3.291139240506329e-05</v>
       </c>
       <c r="X3">
-        <v>0.13630562891089</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AB3">
-        <v>0.1362990775494417</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AD3">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.081</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.013</v>
+        <v>-0.013</v>
       </c>
       <c r="AH3">
-        <v>0.000219881047068117</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.001142760401235874</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>3.529606611767708e-05</v>
+        <v>-3.291247560046279e-05</v>
       </c>
       <c r="AK3">
-        <v>0.0001835821106294042</v>
+        <v>-4.793740112911016e-05</v>
       </c>
       <c r="AL3">
-        <v>0.029</v>
+        <v>0.513</v>
       </c>
       <c r="AM3">
-        <v>-0.778</v>
-      </c>
-      <c r="AN3">
-        <v>0.002040302267002519</v>
+        <v>-62.287</v>
       </c>
       <c r="AO3">
-        <v>1368.965517241379</v>
-      </c>
-      <c r="AP3">
-        <v>0.0003274559193954659</v>
+        <v>515.9844054580897</v>
       </c>
       <c r="AQ3">
-        <v>-51.02827763496144</v>
+        <v>-4.249682919389278</v>
       </c>
     </row>
     <row r="4">
@@ -823,7 +817,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Atlantis Yatirim Holding A.S. (IBSE:ATSYH)</t>
+          <t>Is Girisim Sermayesi Yatirim Ortakligi AS (IBSE:ISGSY)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -832,25 +826,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.337</v>
+        <v>1.527</v>
+      </c>
+      <c r="E4">
+        <v>2.681</v>
       </c>
       <c r="G4">
-        <v>0.007604562737642586</v>
+        <v>1.386524822695036</v>
       </c>
       <c r="H4">
-        <v>0.007604562737642586</v>
+        <v>1.386524822695036</v>
       </c>
       <c r="I4">
-        <v>0.2064638783269962</v>
+        <v>0.9680851063829787</v>
       </c>
       <c r="J4">
-        <v>0.1428871319681389</v>
+        <v>0.9680851063829787</v>
       </c>
       <c r="K4">
-        <v>0.333</v>
+        <v>27.4</v>
       </c>
       <c r="L4">
-        <v>0.1266159695817491</v>
+        <v>0.9716312056737588</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,61 +871,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.003</v>
+        <v>1.88</v>
       </c>
       <c r="V4">
-        <v>6e-05</v>
+        <v>0.0329246935201401</v>
       </c>
       <c r="W4">
-        <v>0.6529411764705882</v>
+        <v>1.838926174496644</v>
       </c>
       <c r="X4">
-        <v>0.1362906208857788</v>
+        <v>0.1109894088519788</v>
       </c>
       <c r="Y4">
-        <v>0.5166505555848095</v>
+        <v>1.727936765644665</v>
+      </c>
+      <c r="Z4">
+        <v>2.233132720937599</v>
+      </c>
+      <c r="AA4">
+        <v>2.161862527716186</v>
       </c>
       <c r="AB4">
-        <v>0.136290025297337</v>
+        <v>0.1109521396568795</v>
+      </c>
+      <c r="AC4">
+        <v>2.050910388059307</v>
       </c>
       <c r="AD4">
-        <v>0.001</v>
+        <v>0.108</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.001</v>
+        <v>0.108</v>
       </c>
       <c r="AG4">
-        <v>-0.002</v>
+        <v>-1.772</v>
       </c>
       <c r="AH4">
-        <v>1.999960000799984e-05</v>
+        <v>0.00188784785344707</v>
       </c>
       <c r="AI4">
-        <v>0.001328021248339974</v>
+        <v>0.002879385731044044</v>
       </c>
       <c r="AJ4">
-        <v>-4.000160006400256e-05</v>
+        <v>-0.03202718334297281</v>
       </c>
       <c r="AK4">
-        <v>-0.002666666666666667</v>
+        <v>-0.04973616256876613</v>
       </c>
       <c r="AL4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.109</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.001814882032667877</v>
+        <v>0.003941605839416058</v>
       </c>
       <c r="AP4">
-        <v>-0.003629764065335753</v>
-      </c>
-      <c r="AQ4">
-        <v>-4.98165137614679</v>
+        <v>-0.06467153284671533</v>
       </c>
     </row>
     <row r="5">
@@ -939,7 +942,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Euro Menkul Kiymet Yatirim Ortakligi Anonim Sirketi (IBSE:EUYO)</t>
+          <t>Atlantis Yatirim Holding A.S. (IBSE:ATSYH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -948,115 +951,118 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.244</v>
+        <v>0.412</v>
       </c>
       <c r="E5">
-        <v>0.201</v>
+        <v>0.892</v>
       </c>
       <c r="G5">
-        <v>0.08950617283950615</v>
+        <v>0.5373831775700934</v>
       </c>
       <c r="H5">
-        <v>0.08950617283950615</v>
+        <v>0.5373831775700934</v>
       </c>
       <c r="I5">
-        <v>0.1080246913580247</v>
+        <v>0.2710280373831775</v>
       </c>
       <c r="J5">
-        <v>0.1080246913580247</v>
+        <v>0.1968903231214115</v>
       </c>
       <c r="K5">
-        <v>0.321</v>
+        <v>0.283</v>
       </c>
       <c r="L5">
-        <v>0.09907407407407406</v>
+        <v>0.1322429906542056</v>
       </c>
       <c r="M5">
-        <v>0.038</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.007421875</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.1183800623052959</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.038</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.007421875</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.1183800623052959</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>2.01</v>
+        <v>0.005</v>
       </c>
       <c r="V5">
-        <v>0.3925781249999999</v>
+        <v>0.0003937007874015749</v>
       </c>
       <c r="W5">
-        <v>0.07262443438914028</v>
+        <v>0.4896193771626298</v>
       </c>
       <c r="X5">
-        <v>0.1362891195533376</v>
+        <v>0.1109424911196242</v>
       </c>
       <c r="Y5">
-        <v>-0.06366468516419733</v>
+        <v>0.3786768860430056</v>
       </c>
       <c r="Z5">
-        <v>14.72727272727274</v>
+        <v>6.993464052287583</v>
       </c>
       <c r="AA5">
-        <v>1.590909090909093</v>
+        <v>1.376945396992878</v>
       </c>
       <c r="AB5">
-        <v>0.1362891195533376</v>
+        <v>0.1109243987324382</v>
       </c>
       <c r="AC5">
-        <v>1.454619971355755</v>
+        <v>1.26602099826044</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="AG5">
-        <v>-2.01</v>
+        <v>0.008</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.00102257531660505</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.01540284360189573</v>
       </c>
       <c r="AJ5">
-        <v>-0.6463022508038584</v>
+        <v>0.0006295247088448223</v>
       </c>
       <c r="AK5">
-        <v>-5.153846153846152</v>
+        <v>0.009535160905840287</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.02229845626072041</v>
+      </c>
+      <c r="AO5">
+        <v>580</v>
       </c>
       <c r="AP5">
-        <v>-5.726495726495727</v>
+        <v>0.0137221269296741</v>
+      </c>
+      <c r="AQ5">
+        <v>580</v>
       </c>
     </row>
     <row r="6">
@@ -1067,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Euro Kapital Yatirim Ortakligi Anonim Sirketi (IBSE:EUKYO)</t>
+          <t>Atlas Menkul Kiymetler Yatirim Ortakligi A.S. (IBSE:ATLAS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1076,46 +1082,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.28</v>
+        <v>0.5660000000000001</v>
       </c>
       <c r="E6">
-        <v>0.17</v>
+        <v>0.748</v>
       </c>
       <c r="G6">
-        <v>0.09205298013245033</v>
+        <v>0.05362718089990817</v>
       </c>
       <c r="H6">
-        <v>0.09205298013245033</v>
+        <v>0.05362718089990817</v>
       </c>
       <c r="I6">
-        <v>0.1043046357615894</v>
+        <v>0.04894398530762167</v>
       </c>
       <c r="J6">
-        <v>0.1043046357615894</v>
+        <v>0.04894398530762167</v>
       </c>
       <c r="K6">
-        <v>0.314</v>
+        <v>5.33</v>
       </c>
       <c r="L6">
-        <v>0.1039735099337748</v>
+        <v>0.04894398530762167</v>
       </c>
       <c r="M6">
-        <v>0.038</v>
+        <v>0.7799999999999999</v>
       </c>
       <c r="N6">
-        <v>0.007169811320754717</v>
+        <v>0.08657047724750276</v>
       </c>
       <c r="O6">
-        <v>0.1210191082802548</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="P6">
-        <v>0.038</v>
+        <v>0.7799999999999999</v>
       </c>
       <c r="Q6">
-        <v>0.007169811320754717</v>
+        <v>0.08657047724750276</v>
       </c>
       <c r="R6">
-        <v>0.1210191082802548</v>
+        <v>0.1463414634146341</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1124,31 +1130,31 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>2.07</v>
+        <v>1.02</v>
       </c>
       <c r="V6">
-        <v>0.390566037735849</v>
+        <v>0.1132075471698113</v>
       </c>
       <c r="W6">
-        <v>0.06796536796536796</v>
+        <v>0.8680781758957655</v>
       </c>
       <c r="X6">
-        <v>0.1362891195533376</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y6">
-        <v>-0.06832375158796965</v>
+        <v>0.7571910272721319</v>
       </c>
       <c r="Z6">
-        <v>14.38095238095238</v>
+        <v>27.1571072319202</v>
       </c>
       <c r="AA6">
-        <v>1.5</v>
+        <v>1.329177057356609</v>
       </c>
       <c r="AB6">
-        <v>0.1362891195533376</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC6">
-        <v>1.363710880446663</v>
+        <v>1.218289908732975</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1160,7 +1166,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-2.07</v>
+        <v>-1.02</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1169,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.6408668730650154</v>
+        <v>-0.1276595744680851</v>
       </c>
       <c r="AK6">
-        <v>-5.048780487804876</v>
+        <v>-0.1197183098591549</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1184,7 +1190,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>-6.489028213166144</v>
+        <v>-0.1913696060037524</v>
       </c>
     </row>
     <row r="7">
@@ -1195,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Euro Trend Yatirim Ortakligi A.S. (IBSE:ETYAT)</t>
+          <t>Metro Yatirim Ortakligi A.S. (IBSE:MTRYO)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1204,46 +1210,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.254</v>
+        <v>0.701</v>
       </c>
       <c r="E7">
-        <v>0.186</v>
+        <v>1.924</v>
       </c>
       <c r="G7">
-        <v>0.07408536585365853</v>
+        <v>0.05513666352497644</v>
       </c>
       <c r="H7">
-        <v>0.07408536585365853</v>
+        <v>0.05513666352497644</v>
       </c>
       <c r="I7">
-        <v>0.08810975609756097</v>
+        <v>0.05042412818096136</v>
       </c>
       <c r="J7">
-        <v>0.08810975609756097</v>
+        <v>0.05042412818096136</v>
       </c>
       <c r="K7">
-        <v>0.284</v>
+        <v>5.35</v>
       </c>
       <c r="L7">
-        <v>0.08658536585365853</v>
+        <v>0.05042412818096136</v>
       </c>
       <c r="M7">
-        <v>0.033</v>
+        <v>0.077</v>
       </c>
       <c r="N7">
-        <v>0.00586145648312611</v>
+        <v>0.007623762376237624</v>
       </c>
       <c r="O7">
-        <v>0.1161971830985916</v>
+        <v>0.01439252336448598</v>
       </c>
       <c r="P7">
-        <v>0.033</v>
+        <v>0.077</v>
       </c>
       <c r="Q7">
-        <v>0.00586145648312611</v>
+        <v>0.007623762376237624</v>
       </c>
       <c r="R7">
-        <v>0.1161971830985916</v>
+        <v>0.01439252336448598</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1252,31 +1258,31 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.91</v>
+        <v>0.947</v>
       </c>
       <c r="V7">
-        <v>0.3392539964476021</v>
+        <v>0.09376237623762376</v>
       </c>
       <c r="W7">
-        <v>0.06558891454965357</v>
+        <v>0.7239512855209743</v>
       </c>
       <c r="X7">
-        <v>0.1362891195533376</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y7">
-        <v>-0.07070020500368404</v>
+        <v>0.6130641368973407</v>
       </c>
       <c r="Z7">
-        <v>16.39999999999998</v>
+        <v>24.96470588235294</v>
       </c>
       <c r="AA7">
-        <v>1.444999999999999</v>
+        <v>1.258823529411765</v>
       </c>
       <c r="AB7">
-        <v>0.1362891195533376</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC7">
-        <v>1.308710880446661</v>
+        <v>1.147936380788131</v>
       </c>
       <c r="AD7">
         <v>0</v>
@@ -1288,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>-1.91</v>
+        <v>-0.947</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1297,10 +1303,10 @@
         <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.5134408602150538</v>
+        <v>-0.1034633453512509</v>
       </c>
       <c r="AK7">
-        <v>-4.658536585365854</v>
+        <v>-0.1096953550330128</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1312,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>-6.586206896551724</v>
+        <v>-0.1770093457943925</v>
       </c>
     </row>
     <row r="8">
@@ -1323,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Güler Yatirim Holding A.S. (IBSE:GLRYH)</t>
+          <t>Euro Kapital Yatirim Ortakligi Anonim Sirketi (IBSE:EUKYO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1332,115 +1338,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.9340000000000001</v>
+        <v>-0.21</v>
+      </c>
+      <c r="E8">
+        <v>0.517</v>
       </c>
       <c r="G8">
-        <v>0.04514931793044119</v>
+        <v>0.1181184668989547</v>
       </c>
       <c r="H8">
-        <v>0.04399655892835197</v>
+        <v>0.1181184668989547</v>
       </c>
       <c r="I8">
-        <v>0.06697800172053582</v>
+        <v>0.1526132404181185</v>
       </c>
       <c r="J8">
-        <v>0.05585463338746064</v>
+        <v>0.1526132404181185</v>
       </c>
       <c r="K8">
-        <v>21.3</v>
+        <v>0.437</v>
       </c>
       <c r="L8">
-        <v>0.02617672360820941</v>
+        <v>0.1522648083623693</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>0.044</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.004271844660194174</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.1006864988558352</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>0.044</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.004271844660194174</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.1006864988558352</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>13.8</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="V8">
-        <v>0.1593533487297922</v>
+        <v>0.05475728155339805</v>
       </c>
       <c r="W8">
-        <v>0.6698113207547169</v>
+        <v>0.1600732600732601</v>
       </c>
       <c r="X8">
-        <v>0.1784165771968134</v>
+        <v>0.111244084990605</v>
       </c>
       <c r="Y8">
-        <v>0.4913947435579036</v>
+        <v>0.04882917508265512</v>
       </c>
       <c r="Z8">
-        <v>24.30188453842249</v>
+        <v>6.999999999999998</v>
       </c>
       <c r="AA8">
-        <v>1.357372851517986</v>
+        <v>1.068292682926829</v>
       </c>
       <c r="AB8">
-        <v>0.1515169179090169</v>
+        <v>0.1111260651349393</v>
       </c>
       <c r="AC8">
-        <v>1.205855933608969</v>
+        <v>0.9571666177918896</v>
       </c>
       <c r="AD8">
-        <v>48.6</v>
+        <v>0.068</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>48.6</v>
+        <v>0.068</v>
       </c>
       <c r="AG8">
-        <v>34.8</v>
+        <v>-0.4959999999999999</v>
       </c>
       <c r="AH8">
-        <v>0.3594674556213018</v>
+        <v>0.006558641975308642</v>
       </c>
       <c r="AI8">
-        <v>0.3441926345609065</v>
+        <v>0.03151065801668212</v>
       </c>
       <c r="AJ8">
-        <v>0.28665568369028</v>
+        <v>-0.05059159526723785</v>
       </c>
       <c r="AK8">
-        <v>0.2731554160125589</v>
+        <v>-0.3111668757841907</v>
       </c>
       <c r="AL8">
-        <v>5.4</v>
+        <v>0.004</v>
       </c>
       <c r="AM8">
-        <v>0.3300000000000001</v>
+        <v>0.004</v>
       </c>
       <c r="AN8">
-        <v>0.8868613138686132</v>
+        <v>0.1541950113378685</v>
       </c>
       <c r="AO8">
-        <v>10.09259259259259</v>
+        <v>109.5</v>
       </c>
       <c r="AP8">
-        <v>0.635036496350365</v>
+        <v>-1.124716553287982</v>
       </c>
       <c r="AQ8">
-        <v>165.1515151515151</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="9">
@@ -1451,7 +1463,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Birikim Varlik Yonetim Anonim Sirketi (IBSE:BRKVY)</t>
+          <t>Euro Menkul Kiymet Yatirim Ortakligi Anonim Sirketi (IBSE:EUYO)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1459,113 +1471,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.209</v>
+      </c>
+      <c r="E9">
+        <v>0.614</v>
+      </c>
       <c r="G9">
-        <v>0.4906832298136646</v>
+        <v>0.1292857142857143</v>
       </c>
       <c r="H9">
-        <v>0.4906832298136646</v>
+        <v>0.1292857142857143</v>
       </c>
       <c r="I9">
-        <v>0.5714285714285713</v>
+        <v>0.1557142857142857</v>
       </c>
       <c r="J9">
-        <v>0.4425249169435215</v>
+        <v>0.1557142857142857</v>
       </c>
       <c r="K9">
-        <v>13.3</v>
+        <v>0.422</v>
       </c>
       <c r="L9">
-        <v>0.4130434782608696</v>
+        <v>0.1507142857142857</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>0.047</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.005683192261185006</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.1113744075829384</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>0.047</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.005683192261185006</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.1113744075829384</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>2.74</v>
+        <v>0.412</v>
       </c>
       <c r="V9">
-        <v>0.02582469368520264</v>
+        <v>0.0498186215235792</v>
       </c>
       <c r="W9">
-        <v>1.366906474820144</v>
+        <v>0.1604562737642586</v>
       </c>
       <c r="X9">
-        <v>0.1424232158137158</v>
+        <v>0.111312087982207</v>
       </c>
       <c r="Y9">
-        <v>1.224483259006428</v>
+        <v>0.04914418578205157</v>
       </c>
       <c r="Z9">
-        <v>1.758601856908793</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="AA9">
-        <v>0.7782251406652863</v>
+        <v>1.038095238095238</v>
       </c>
       <c r="AB9">
-        <v>0.1397102912579481</v>
+        <v>0.1111712281876604</v>
       </c>
       <c r="AC9">
-        <v>0.6385148494073382</v>
+        <v>0.9269240099075777</v>
       </c>
       <c r="AD9">
-        <v>8.67</v>
+        <v>0.065</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>8.67</v>
+        <v>0.065</v>
       </c>
       <c r="AG9">
-        <v>5.93</v>
+        <v>-0.347</v>
       </c>
       <c r="AH9">
-        <v>0.07554238912607825</v>
+        <v>0.007798440311937614</v>
       </c>
       <c r="AI9">
-        <v>0.3202807536017732</v>
+        <v>0.0314769975786925</v>
       </c>
       <c r="AJ9">
-        <v>0.05293225029010086</v>
+        <v>-0.04379654171399722</v>
       </c>
       <c r="AK9">
-        <v>0.2437320180846691</v>
+        <v>-0.2099213551119177</v>
       </c>
       <c r="AL9">
-        <v>1.3</v>
+        <v>0.006</v>
       </c>
       <c r="AM9">
-        <v>1.3</v>
+        <v>0.006</v>
       </c>
       <c r="AN9">
-        <v>0.4711956521739131</v>
+        <v>0.1457399103139013</v>
       </c>
       <c r="AO9">
-        <v>14.15384615384615</v>
+        <v>72.66666666666667</v>
       </c>
       <c r="AP9">
-        <v>0.3222826086956522</v>
+        <v>-0.7780269058295963</v>
       </c>
       <c r="AQ9">
-        <v>14.15384615384615</v>
+        <v>72.66666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -1576,7 +1597,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Atlas Menkul Kiymetler Yatirim Ortakligi A.S. (IBSE:ATLAS)</t>
+          <t>Euro Trend Yatirim Ortakligi A.S. (IBSE:ETYAT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,46 +1606,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0525</v>
+        <v>-0.193</v>
       </c>
       <c r="E10">
-        <v>0.531</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="G10">
-        <v>0.02061440677966101</v>
+        <v>0.1043333333333333</v>
       </c>
       <c r="H10">
-        <v>0.02061440677966101</v>
+        <v>0.1043333333333333</v>
       </c>
       <c r="I10">
-        <v>0.06673728813559321</v>
+        <v>0.1353333333333333</v>
       </c>
       <c r="J10">
-        <v>0.06673728813559321</v>
+        <v>0.1353333333333333</v>
       </c>
       <c r="K10">
-        <v>3.13</v>
+        <v>0.4</v>
       </c>
       <c r="L10">
-        <v>0.06631355932203389</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="M10">
-        <v>0.127</v>
+        <v>0.04</v>
       </c>
       <c r="N10">
-        <v>0.01104347826086957</v>
+        <v>0.00631911532385466</v>
       </c>
       <c r="O10">
-        <v>0.04057507987220448</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="P10">
-        <v>0.127</v>
+        <v>0.04</v>
       </c>
       <c r="Q10">
-        <v>0.01104347826086957</v>
+        <v>0.00631911532385466</v>
       </c>
       <c r="R10">
-        <v>0.04057507987220448</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1633,67 +1654,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>3.27</v>
+        <v>0.43</v>
       </c>
       <c r="V10">
-        <v>0.2843478260869565</v>
+        <v>0.0679304897314376</v>
       </c>
       <c r="W10">
-        <v>0.343956043956044</v>
+        <v>0.1724137931034483</v>
       </c>
       <c r="X10">
-        <v>0.1362891195533376</v>
+        <v>0.1114423221616118</v>
       </c>
       <c r="Y10">
-        <v>0.2076669244027063</v>
+        <v>0.06097147094183648</v>
       </c>
       <c r="Z10">
-        <v>11.37349397590362</v>
+        <v>7.317073170731708</v>
       </c>
       <c r="AA10">
-        <v>0.7590361445783134</v>
+        <v>0.9902439024390246</v>
       </c>
       <c r="AB10">
-        <v>0.1362891195533376</v>
+        <v>0.111257407132807</v>
       </c>
       <c r="AC10">
-        <v>0.6227470250249758</v>
+        <v>0.8789864953062176</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>0.065</v>
       </c>
       <c r="AG10">
-        <v>-3.27</v>
+        <v>-0.365</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.01016419077404222</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.03258145363408522</v>
       </c>
       <c r="AJ10">
-        <v>-0.3973268529769137</v>
+        <v>-0.06119027661357921</v>
       </c>
       <c r="AK10">
-        <v>-0.7995110024449879</v>
+        <v>-0.2332268370607029</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>-0.004</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>0.1597051597051597</v>
+      </c>
+      <c r="AO10">
+        <v>67.66666666666667</v>
       </c>
       <c r="AP10">
-        <v>-1.038095238095238</v>
+        <v>-0.8968058968058968</v>
+      </c>
+      <c r="AQ10">
+        <v>-101.5</v>
       </c>
     </row>
     <row r="11">
@@ -1704,7 +1731,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Metro Yatirim Ortakligi A.S. (IBSE:MTRYO)</t>
+          <t>Hedef Holding A.S (IBSE:HEDEF)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1712,116 +1739,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D11">
-        <v>0.611</v>
-      </c>
-      <c r="E11">
-        <v>0.7709999999999999</v>
-      </c>
       <c r="G11">
-        <v>0.02004739336492891</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="H11">
-        <v>0.02004739336492891</v>
+        <v>1.541666666666667</v>
       </c>
       <c r="I11">
-        <v>0.07440758293838862</v>
+        <v>0.9873188405797101</v>
       </c>
       <c r="J11">
-        <v>0.07440758293838862</v>
+        <v>0.7833571788146146</v>
       </c>
       <c r="K11">
-        <v>3.14</v>
+        <v>43.4</v>
       </c>
       <c r="L11">
-        <v>0.07440758293838862</v>
+        <v>0.786231884057971</v>
       </c>
       <c r="M11">
-        <v>0.126</v>
+        <v>0.377</v>
       </c>
       <c r="N11">
-        <v>0.01461716937354988</v>
+        <v>0.001066478076379067</v>
       </c>
       <c r="O11">
-        <v>0.04012738853503185</v>
+        <v>0.008686635944700462</v>
       </c>
       <c r="P11">
-        <v>0.126</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.01461716937354988</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.04012738853503185</v>
+        <v>-0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>0.377</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U11">
-        <v>3.14</v>
+        <v>0.187</v>
       </c>
       <c r="V11">
-        <v>0.3642691415313226</v>
+        <v>0.000528995756718529</v>
       </c>
       <c r="W11">
-        <v>0.3442982456140351</v>
+        <v>0.6129943502824858</v>
       </c>
       <c r="X11">
-        <v>0.1362891195533376</v>
+        <v>0.1109134548249701</v>
       </c>
       <c r="Y11">
-        <v>0.2080091260606975</v>
+        <v>0.5020808954575158</v>
       </c>
       <c r="Z11">
-        <v>10.04761904761905</v>
+        <v>0.7795178851340856</v>
       </c>
       <c r="AA11">
-        <v>0.7476190476190477</v>
+        <v>0.6106409313341721</v>
       </c>
       <c r="AB11">
-        <v>0.1362891195533376</v>
+        <v>0.110903890888939</v>
       </c>
       <c r="AC11">
-        <v>0.6113299280657101</v>
+        <v>0.4997370404452331</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>0.172</v>
       </c>
       <c r="AG11">
-        <v>-3.14</v>
+        <v>-0.01500000000000001</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>0.0004863263136465425</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>0.001888615600843289</v>
       </c>
       <c r="AJ11">
-        <v>-0.5729927007299271</v>
+        <v>-4.243461533021207e-05</v>
       </c>
       <c r="AK11">
-        <v>-0.7388235294117648</v>
+        <v>-0.0001650437365901966</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-0.114</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>0.003155963302752293</v>
+      </c>
+      <c r="AO11">
+        <v>2868.421052631579</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>-0.0002752293577981654</v>
+      </c>
+      <c r="AQ11">
+        <v>-478.0701754385965</v>
       </c>
     </row>
     <row r="12">
@@ -1832,7 +1859,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oyak Yatirim Ortakligi AS (IBSE:OYAYO)</t>
+          <t>Hedef Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HDFGS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1841,115 +1868,118 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.169</v>
+        <v>0.419</v>
       </c>
       <c r="E12">
-        <v>0.677</v>
+        <v>0.575</v>
       </c>
       <c r="G12">
-        <v>0.04176991150442477</v>
+        <v>1.570048309178744</v>
       </c>
       <c r="H12">
-        <v>0.04176991150442477</v>
+        <v>1.570048309178744</v>
       </c>
       <c r="I12">
-        <v>0.09823008849557523</v>
+        <v>0.9516908212560387</v>
       </c>
       <c r="J12">
-        <v>0.09823008849557523</v>
+        <v>0.9516908212560387</v>
       </c>
       <c r="K12">
-        <v>1.11</v>
+        <v>21.7</v>
       </c>
       <c r="L12">
-        <v>0.09823008849557523</v>
+        <v>1.048309178743961</v>
       </c>
       <c r="M12">
-        <v>0.063</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.00443661971830986</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.05675675675675675</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>0.063</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.00443661971830986</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.05675675675675675</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.354</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V12">
-        <v>0.02492957746478873</v>
+        <v>0.000263157894736842</v>
       </c>
       <c r="W12">
-        <v>0.2642857142857143</v>
+        <v>0.6112676056338028</v>
       </c>
       <c r="X12">
-        <v>0.1362891195533376</v>
+        <v>0.1109314126622621</v>
       </c>
       <c r="Y12">
-        <v>0.1279965947323767</v>
+        <v>0.5003361929715406</v>
       </c>
       <c r="Z12">
-        <v>2.967436974789916</v>
+        <v>0.5826062482409232</v>
       </c>
       <c r="AA12">
-        <v>0.2914915966386555</v>
+        <v>0.5544610188573038</v>
       </c>
       <c r="AB12">
-        <v>0.1362891195533376</v>
+        <v>0.1109169481079301</v>
       </c>
       <c r="AC12">
-        <v>0.1552024770853179</v>
+        <v>0.4435440707493737</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>0.028</v>
       </c>
       <c r="AG12">
-        <v>-0.354</v>
+        <v>0.019</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.0008180437069066262</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.0005878894767783657</v>
       </c>
       <c r="AJ12">
-        <v>-0.02556695074389715</v>
+        <v>0.000555247084952804</v>
       </c>
       <c r="AK12">
-        <v>-0.130820399113082</v>
+        <v>0.0003990003990003991</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>-1.769</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>0.001421319796954315</v>
+      </c>
+      <c r="AO12">
+        <v>19700</v>
       </c>
       <c r="AP12">
-        <v>-0.3189189189189189</v>
+        <v>0.0009644670050761423</v>
+      </c>
+      <c r="AQ12">
+        <v>-11.13623516110797</v>
       </c>
     </row>
     <row r="13">
@@ -1960,7 +1990,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deniz Gayrimenkul Yatirim Ortakligi A.S. (IBSE:DZGYO)</t>
+          <t>Güler Yatirim Holding A.S. (IBSE:GLRYH)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1969,28 +1999,28 @@
         </is>
       </c>
       <c r="D13">
-        <v>1.284</v>
+        <v>0.662</v>
       </c>
       <c r="E13">
-        <v>0.862</v>
+        <v>1.13</v>
       </c>
       <c r="G13">
-        <v>0.2719298245614035</v>
+        <v>0.1028926185990752</v>
       </c>
       <c r="H13">
-        <v>0.2719298245614035</v>
+        <v>0.1024147970542901</v>
       </c>
       <c r="I13">
-        <v>0.3991228070175438</v>
+        <v>0.08665867443055318</v>
       </c>
       <c r="J13">
-        <v>0.3991228070175438</v>
+        <v>0.06684568690049081</v>
       </c>
       <c r="K13">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="L13">
-        <v>0.4035087719298245</v>
+        <v>0.03082719643774619</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2014,73 +2044,73 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>19.3</v>
+        <v>45.7</v>
       </c>
       <c r="V13">
-        <v>0.2218390804597701</v>
+        <v>1.036281179138322</v>
       </c>
       <c r="W13">
-        <v>0.2555555555555555</v>
+        <v>0.4699738903394256</v>
       </c>
       <c r="X13">
-        <v>0.1364030137385261</v>
+        <v>0.1547769431938051</v>
       </c>
       <c r="Y13">
-        <v>0.1191525418170294</v>
+        <v>0.3151969471456205</v>
       </c>
       <c r="Z13">
-        <v>0.7078656917990035</v>
+        <v>8.014879481688903</v>
       </c>
       <c r="AA13">
-        <v>0.2825253419022338</v>
+        <v>0.5357601243781445</v>
       </c>
       <c r="AB13">
-        <v>0.1363577284450676</v>
+        <v>0.1263120607442981</v>
       </c>
       <c r="AC13">
-        <v>0.1461676134571663</v>
+        <v>0.4094480636338463</v>
       </c>
       <c r="AD13">
-        <v>0.132</v>
+        <v>35.8</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0.132</v>
+        <v>35.8</v>
       </c>
       <c r="AG13">
-        <v>-19.168</v>
+        <v>-9.900000000000006</v>
       </c>
       <c r="AH13">
-        <v>0.001514942845338108</v>
+        <v>0.4480600750938672</v>
       </c>
       <c r="AI13">
-        <v>0.00248906320712023</v>
+        <v>0.2112094395280236</v>
       </c>
       <c r="AJ13">
-        <v>-0.2825804929826631</v>
+        <v>-0.2894736842105265</v>
       </c>
       <c r="AK13">
-        <v>-0.568243804102929</v>
+        <v>-0.07996768982229407</v>
       </c>
       <c r="AL13">
-        <v>3.46</v>
+        <v>13.2</v>
       </c>
       <c r="AM13">
-        <v>1.11</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="AN13">
-        <v>0.007173913043478261</v>
+        <v>0.6911196911196911</v>
       </c>
       <c r="AO13">
-        <v>5.260115606936416</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="AP13">
-        <v>-1.041739130434783</v>
+        <v>-0.1911196911196912</v>
       </c>
       <c r="AQ13">
-        <v>16.3963963963964</v>
+        <v>12.52475247524753</v>
       </c>
     </row>
     <row r="14">
@@ -2091,7 +2121,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Marka Yatirim Holding A.S. (IBSE:MARKA)</t>
+          <t>Oyak Yatirim Ortakligi AS (IBSE:OYAYO)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2100,115 +2130,115 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.482</v>
+        <v>0.501</v>
       </c>
       <c r="E14">
-        <v>0.268</v>
+        <v>0.755</v>
       </c>
       <c r="G14">
-        <v>-0.50873786407767</v>
+        <v>0.1042553191489362</v>
       </c>
       <c r="H14">
-        <v>-0.50873786407767</v>
+        <v>0.1042553191489362</v>
       </c>
       <c r="I14">
-        <v>0.2631067961165049</v>
+        <v>0.09432624113475178</v>
       </c>
       <c r="J14">
-        <v>0.2041012278697887</v>
+        <v>0.09432624113475178</v>
       </c>
       <c r="K14">
-        <v>0.259</v>
+        <v>1.33</v>
       </c>
       <c r="L14">
-        <v>0.2514563106796117</v>
+        <v>0.09432624113475178</v>
       </c>
       <c r="M14">
-        <v>-0</v>
+        <v>0.191</v>
       </c>
       <c r="N14">
-        <v>-0</v>
+        <v>0.01186335403726708</v>
       </c>
       <c r="O14">
-        <v>-0</v>
+        <v>0.143609022556391</v>
       </c>
       <c r="P14">
-        <v>-0</v>
+        <v>0.191</v>
       </c>
       <c r="Q14">
-        <v>-0</v>
+        <v>0.01186335403726708</v>
       </c>
       <c r="R14">
-        <v>-0</v>
+        <v>0.143609022556391</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
       <c r="U14">
-        <v>0.068</v>
+        <v>0.318</v>
       </c>
       <c r="V14">
-        <v>0.01207815275310835</v>
+        <v>0.01975155279503105</v>
       </c>
       <c r="W14">
-        <v>0.1497109826589595</v>
+        <v>0.434640522875817</v>
       </c>
       <c r="X14">
-        <v>0.1366357860139873</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y14">
-        <v>0.01307519664497223</v>
+        <v>0.3237533742521834</v>
       </c>
       <c r="Z14">
-        <v>1.154708520179372</v>
+        <v>5.210643015521065</v>
       </c>
       <c r="AA14">
-        <v>0.2356774268003165</v>
+        <v>0.4915003695491501</v>
       </c>
       <c r="AB14">
-        <v>0.1364838534197728</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC14">
-        <v>0.09919357338054374</v>
+        <v>0.3806132209255165</v>
       </c>
       <c r="AD14">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>-0.04200000000000001</v>
+        <v>-0.318</v>
       </c>
       <c r="AH14">
-        <v>0.004596888260254597</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>0.02394106813996317</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.007516105941302793</v>
+        <v>-0.02014953744772525</v>
       </c>
       <c r="AK14">
-        <v>-0.04125736738703341</v>
+        <v>-0.1103400416377516</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>0.08843537414965986</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>-0.1428571428571429</v>
-      </c>
-      <c r="AQ14">
-        <v>-54.2</v>
+        <v>-0.2390977443609023</v>
       </c>
     </row>
     <row r="15">
@@ -2219,7 +2249,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Is Yatirim Ortakligi A.S. (IBSE:ISYAT)</t>
+          <t>Birikim Varlik Yonetim Anonim Sirketi (IBSE:BRKVY)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2227,47 +2257,41 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D15">
-        <v>-0.124</v>
-      </c>
-      <c r="E15">
-        <v>0.261</v>
-      </c>
       <c r="G15">
-        <v>0.2156424581005587</v>
+        <v>0.4573643410852714</v>
       </c>
       <c r="H15">
-        <v>0.2156424581005587</v>
+        <v>0.4573643410852714</v>
       </c>
       <c r="I15">
-        <v>0.2418994413407821</v>
+        <v>0.5503875968992248</v>
       </c>
       <c r="J15">
-        <v>0.2418994413407821</v>
+        <v>0.4372523686477175</v>
       </c>
       <c r="K15">
-        <v>4.33</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>0.2418994413407821</v>
+        <v>0.3875968992248062</v>
       </c>
       <c r="M15">
-        <v>2.17</v>
+        <v>0.901</v>
       </c>
       <c r="N15">
-        <v>0.04909502262443438</v>
+        <v>0.01022701475595914</v>
       </c>
       <c r="O15">
-        <v>0.5011547344110854</v>
+        <v>0.0901</v>
       </c>
       <c r="P15">
-        <v>2.17</v>
+        <v>0.901</v>
       </c>
       <c r="Q15">
-        <v>0.04909502262443438</v>
+        <v>0.01022701475595914</v>
       </c>
       <c r="R15">
-        <v>0.5011547344110854</v>
+        <v>0.0901</v>
       </c>
       <c r="S15">
         <v>0</v>
@@ -2276,73 +2300,73 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>0.649</v>
+        <v>2.05</v>
       </c>
       <c r="V15">
-        <v>0.01468325791855204</v>
+        <v>0.02326901248581158</v>
       </c>
       <c r="W15">
-        <v>0.1557553956834532</v>
+        <v>0.5434782608695653</v>
       </c>
       <c r="X15">
-        <v>0.1363723382067482</v>
+        <v>0.1147410699632172</v>
       </c>
       <c r="Y15">
-        <v>0.01938305747670505</v>
+        <v>0.4287371909063481</v>
       </c>
       <c r="Z15">
-        <v>0.7734520157282979</v>
+        <v>1.060419235511714</v>
       </c>
       <c r="AA15">
-        <v>0.1870976105085771</v>
+        <v>0.4636708224870987</v>
       </c>
       <c r="AB15">
-        <v>0.1363294644691543</v>
+        <v>0.1133110330651727</v>
       </c>
       <c r="AC15">
-        <v>0.05076814603942278</v>
+        <v>0.350359789421926</v>
       </c>
       <c r="AD15">
-        <v>0.049</v>
+        <v>6.28</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.049</v>
+        <v>6.28</v>
       </c>
       <c r="AG15">
-        <v>-0.6</v>
+        <v>4.23</v>
       </c>
       <c r="AH15">
-        <v>0.001107369658071369</v>
+        <v>0.06653952108497564</v>
       </c>
       <c r="AI15">
-        <v>0.003151328059682295</v>
+        <v>0.2033678756476684</v>
       </c>
       <c r="AJ15">
-        <v>-0.01376146788990826</v>
+        <v>0.04581392830066068</v>
       </c>
       <c r="AK15">
-        <v>-0.04026845637583892</v>
+        <v>0.1467221644120708</v>
       </c>
       <c r="AL15">
-        <v>0.007</v>
+        <v>3.31</v>
       </c>
       <c r="AM15">
-        <v>0.007</v>
+        <v>3.036</v>
       </c>
       <c r="AN15">
-        <v>0.01129032258064516</v>
+        <v>0.4391608391608391</v>
       </c>
       <c r="AO15">
-        <v>618.5714285714286</v>
+        <v>4.290030211480362</v>
       </c>
       <c r="AP15">
-        <v>-0.1382488479262673</v>
+        <v>0.2958041958041958</v>
       </c>
       <c r="AQ15">
-        <v>618.5714285714286</v>
+        <v>4.677206851119895</v>
       </c>
     </row>
     <row r="16">
@@ -2362,46 +2386,46 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.201</v>
+        <v>0.42</v>
       </c>
       <c r="E16">
-        <v>0.462</v>
+        <v>0.47</v>
       </c>
       <c r="G16">
-        <v>0.007435897435897436</v>
+        <v>0.0833574529667149</v>
       </c>
       <c r="H16">
-        <v>0.007435897435897436</v>
+        <v>0.0833574529667149</v>
       </c>
       <c r="I16">
-        <v>0.04170940170940171</v>
+        <v>0.08523878437047756</v>
       </c>
       <c r="J16">
-        <v>0.04170940170940171</v>
+        <v>0.08523878437047756</v>
       </c>
       <c r="K16">
-        <v>0.491</v>
+        <v>0.581</v>
       </c>
       <c r="L16">
-        <v>0.04196581196581197</v>
+        <v>0.08408104196816207</v>
       </c>
       <c r="M16">
-        <v>0.022</v>
+        <v>0.077</v>
       </c>
       <c r="N16">
-        <v>0.002340425531914893</v>
+        <v>0.00909090909090909</v>
       </c>
       <c r="O16">
-        <v>0.04480651731160896</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="P16">
-        <v>0.022</v>
+        <v>0.077</v>
       </c>
       <c r="Q16">
-        <v>0.002340425531914893</v>
+        <v>0.00909090909090909</v>
       </c>
       <c r="R16">
-        <v>0.04480651731160896</v>
+        <v>0.1325301204819277</v>
       </c>
       <c r="S16">
         <v>0</v>
@@ -2410,55 +2434,55 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>0.111</v>
+        <v>0.157</v>
       </c>
       <c r="V16">
-        <v>0.01180851063829787</v>
+        <v>0.01853600944510035</v>
       </c>
       <c r="W16">
-        <v>0.1049145299145299</v>
+        <v>0.2017361111111111</v>
       </c>
       <c r="X16">
-        <v>0.136392935094479</v>
+        <v>0.1109062981023117</v>
       </c>
       <c r="Y16">
-        <v>-0.03147840517994906</v>
+        <v>0.09082981300879946</v>
       </c>
       <c r="Z16">
-        <v>2.717138875986995</v>
+        <v>3.024070021881838</v>
       </c>
       <c r="AA16">
-        <v>0.1133302368787738</v>
+        <v>0.2577680525164113</v>
       </c>
       <c r="AB16">
-        <v>0.1363476245330761</v>
+        <v>0.1108993376916206</v>
       </c>
       <c r="AC16">
-        <v>-0.02301738765430233</v>
+        <v>0.1468687148247907</v>
       </c>
       <c r="AD16">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0.013</v>
+        <v>0.003</v>
       </c>
       <c r="AG16">
-        <v>-0.098</v>
+        <v>-0.154</v>
       </c>
       <c r="AH16">
-        <v>0.001381068734728567</v>
+        <v>0.0003540658562492623</v>
       </c>
       <c r="AI16">
-        <v>0.004774146162320969</v>
+        <v>0.001285897985426489</v>
       </c>
       <c r="AJ16">
-        <v>-0.01053536873790583</v>
+        <v>-0.01851851851851852</v>
       </c>
       <c r="AK16">
-        <v>-0.03751914241960184</v>
+        <v>-0.07077205882352941</v>
       </c>
       <c r="AL16">
         <v>0.003</v>
@@ -2467,16 +2491,16 @@
         <v>0.003</v>
       </c>
       <c r="AN16">
-        <v>0.02653061224489796</v>
+        <v>0.005084745762711865</v>
       </c>
       <c r="AO16">
-        <v>162.6666666666667</v>
+        <v>196.3333333333333</v>
       </c>
       <c r="AP16">
-        <v>-0.2</v>
+        <v>-0.2610169491525424</v>
       </c>
       <c r="AQ16">
-        <v>162.6666666666667</v>
+        <v>196.3333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -2487,7 +2511,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dagi Yatirim Holding A.S. (IBSE:DAGHL)</t>
+          <t>Vakif Menkul Kiymet Yatirim Ortakligi A.S. (IBSE:VKFYO)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2496,109 +2520,118 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.8809999999999999</v>
+        <v>0.028</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>0.06301652892561983</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>0.06301652892561983</v>
       </c>
       <c r="I17">
-        <v>0.02050279329608939</v>
+        <v>0.07541322314049587</v>
       </c>
       <c r="J17">
-        <v>0.01913594040968343</v>
+        <v>0.07541322314049587</v>
       </c>
       <c r="K17">
-        <v>1.2</v>
+        <v>0.365</v>
       </c>
       <c r="L17">
-        <v>0.0670391061452514</v>
+        <v>0.07541322314049587</v>
       </c>
       <c r="M17">
-        <v>-0</v>
+        <v>0.016</v>
       </c>
       <c r="N17">
-        <v>-0</v>
+        <v>0.0006349206349206349</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0.04383561643835616</v>
       </c>
       <c r="P17">
-        <v>-0</v>
+        <v>0.016</v>
       </c>
       <c r="Q17">
-        <v>-0</v>
+        <v>0.0006349206349206349</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0.04383561643835616</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
       <c r="U17">
-        <v>0.03</v>
+        <v>0.238</v>
       </c>
       <c r="V17">
-        <v>0.00160427807486631</v>
+        <v>0.009444444444444445</v>
       </c>
       <c r="W17">
-        <v>0.3571428571428572</v>
+        <v>0.1901041666666667</v>
       </c>
       <c r="X17">
-        <v>0.1420696508774414</v>
+        <v>0.1109043122304487</v>
       </c>
       <c r="Y17">
-        <v>0.2150732062654158</v>
+        <v>0.07919985443621792</v>
       </c>
       <c r="Z17">
-        <v>5.519580635214307</v>
+        <v>2.577209797657082</v>
       </c>
       <c r="AA17">
-        <v>0.1056223661219036</v>
+        <v>0.1943556975505857</v>
       </c>
       <c r="AB17">
-        <v>0.1395271966252238</v>
+        <v>0.1108987093158005</v>
       </c>
       <c r="AC17">
-        <v>-0.03390483050332022</v>
+        <v>0.08345698823478524</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>0.008</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.44</v>
+        <v>0.008</v>
       </c>
       <c r="AG17">
-        <v>1.41</v>
+        <v>-0.23</v>
       </c>
       <c r="AH17">
-        <v>0.0714995034756703</v>
+        <v>0.000317359568390987</v>
       </c>
       <c r="AI17">
-        <v>0.6554392353208921</v>
+        <v>0.004975124378109453</v>
       </c>
       <c r="AJ17">
-        <v>0.07011437095972153</v>
+        <v>-0.0092110532639167</v>
       </c>
       <c r="AK17">
-        <v>0.6506691278264882</v>
+        <v>-0.1678832116788321</v>
       </c>
       <c r="AL17">
-        <v>0.26</v>
+        <v>0.001</v>
       </c>
       <c r="AM17">
-        <v>0.05300000000000002</v>
+        <v>0.001</v>
+      </c>
+      <c r="AN17">
+        <v>0.02203856749311295</v>
       </c>
       <c r="AO17">
-        <v>1.411538461538461</v>
+        <v>365</v>
+      </c>
+      <c r="AP17">
+        <v>-0.6336088154269972</v>
       </c>
       <c r="AQ17">
-        <v>6.92452830188679</v>
+        <v>365</v>
       </c>
     </row>
     <row r="18">
@@ -2609,7 +2642,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vakif Menkul Kiymet Yatirim Ortakligi A.S. (IBSE:VKFYO)</t>
+          <t>Deniz Gayrimenkul Yatirim Ortakligi A.S. (IBSE:DZGYO)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2618,112 +2651,118 @@
         </is>
       </c>
       <c r="D18">
-        <v>-0.0544</v>
+        <v>0.946</v>
+      </c>
+      <c r="E18">
+        <v>1.031</v>
       </c>
       <c r="G18">
-        <v>0.02925925925925926</v>
+        <v>0.9448275862068966</v>
       </c>
       <c r="H18">
-        <v>0.02925925925925926</v>
+        <v>0.9448275862068966</v>
       </c>
       <c r="I18">
-        <v>0.02876543209876543</v>
+        <v>0.436551724137931</v>
       </c>
       <c r="J18">
-        <v>0.02876543209876543</v>
+        <v>0.436551724137931</v>
       </c>
       <c r="K18">
-        <v>0.234</v>
+        <v>26.4</v>
       </c>
       <c r="L18">
-        <v>0.02888888888888889</v>
+        <v>1.820689655172414</v>
       </c>
       <c r="M18">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="N18">
-        <v>0.002307692307692307</v>
+        <v>-0</v>
       </c>
       <c r="O18">
-        <v>0.1282051282051282</v>
+        <v>-0</v>
       </c>
       <c r="P18">
-        <v>0.03</v>
+        <v>-0</v>
       </c>
       <c r="Q18">
-        <v>0.002307692307692307</v>
+        <v>-0</v>
       </c>
       <c r="R18">
-        <v>0.1282051282051282</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
       <c r="U18">
-        <v>0.044</v>
+        <v>0.127</v>
       </c>
       <c r="V18">
-        <v>0.003384615384615384</v>
+        <v>0.002451737451737452</v>
       </c>
       <c r="W18">
-        <v>0.06628895184135979</v>
+        <v>0.499054820415879</v>
       </c>
       <c r="X18">
-        <v>0.1363006682644232</v>
+        <v>0.1109883907097797</v>
       </c>
       <c r="Y18">
-        <v>-0.07001171642306338</v>
+        <v>0.3880664297060993</v>
       </c>
       <c r="Z18">
-        <v>3.095147115017196</v>
+        <v>0.4298588877030713</v>
       </c>
       <c r="AA18">
-        <v>0.08903324417271687</v>
+        <v>0.1876556385627891</v>
       </c>
       <c r="AB18">
-        <v>0.1362956357978713</v>
+        <v>0.1109552352351668</v>
       </c>
       <c r="AC18">
-        <v>-0.04726239162515446</v>
+        <v>0.07670040332762229</v>
       </c>
       <c r="AD18">
-        <v>0.002</v>
+        <v>0.097</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.002</v>
+        <v>0.097</v>
       </c>
       <c r="AG18">
-        <v>-0.042</v>
+        <v>-0.03</v>
       </c>
       <c r="AH18">
-        <v>0.0001538224888478696</v>
+        <v>0.001869086845097019</v>
       </c>
       <c r="AI18">
-        <v>0.001040582726326743</v>
+        <v>0.001557057322182449</v>
       </c>
       <c r="AJ18">
-        <v>-0.00324124093224263</v>
+        <v>-0.0005794861889124976</v>
       </c>
       <c r="AK18">
-        <v>-0.02236421725239617</v>
+        <v>-0.0004825478526620556</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>0.026</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>-8.064</v>
       </c>
       <c r="AN18">
-        <v>0.008547008547008546</v>
+        <v>0.01520376175548589</v>
+      </c>
+      <c r="AO18">
+        <v>243.4615384615385</v>
       </c>
       <c r="AP18">
-        <v>-0.1794871794871795</v>
+        <v>-0.004702194357366771</v>
+      </c>
+      <c r="AQ18">
+        <v>-0.7849702380952381</v>
       </c>
     </row>
     <row r="19">
@@ -2734,7 +2773,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Is Girisim Sermayesi Yatirim Ortakligi AS (IBSE:ISGSY)</t>
+          <t>Verusa Holding A.S. (IBSE:VERUS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2743,109 +2782,121 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.185</v>
+        <v>0.338</v>
+      </c>
+      <c r="E19">
+        <v>0.8640000000000001</v>
       </c>
       <c r="G19">
-        <v>0.6642335766423357</v>
+        <v>0.2018292682926829</v>
       </c>
       <c r="H19">
-        <v>0.6642335766423357</v>
+        <v>0.2018292682926829</v>
       </c>
       <c r="I19">
-        <v>0.4861313868613139</v>
+        <v>0.01817073170731708</v>
       </c>
       <c r="J19">
-        <v>0.4861313868613139</v>
+        <v>0.01682475158084915</v>
       </c>
       <c r="K19">
-        <v>0.666</v>
+        <v>26</v>
       </c>
       <c r="L19">
-        <v>0.4861313868613139</v>
+        <v>1.585365853658537</v>
       </c>
       <c r="M19">
-        <v>-0</v>
+        <v>5.873</v>
       </c>
       <c r="N19">
-        <v>-0</v>
+        <v>0.0125948959897062</v>
       </c>
       <c r="O19">
-        <v>-0</v>
+        <v>0.2258846153846154</v>
       </c>
       <c r="P19">
-        <v>-0</v>
+        <v>0.123</v>
       </c>
       <c r="Q19">
-        <v>-0</v>
+        <v>0.0002637786832511259</v>
       </c>
       <c r="R19">
-        <v>-0</v>
+        <v>0.004730769230769231</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>5.75</v>
+      </c>
+      <c r="T19">
+        <v>0.9790567001532436</v>
       </c>
       <c r="U19">
-        <v>2.35</v>
+        <v>27.1</v>
       </c>
       <c r="V19">
-        <v>0.03415697674418605</v>
+        <v>0.05811709200085782</v>
       </c>
       <c r="W19">
-        <v>0.02242424242424243</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="X19">
-        <v>0.1363742241539245</v>
+        <v>0.1114181787662932</v>
       </c>
       <c r="Y19">
-        <v>-0.113949981729682</v>
+        <v>0.3141137361273239</v>
       </c>
       <c r="Z19">
-        <v>0.05837736492244759</v>
+        <v>0.2456560814859197</v>
       </c>
       <c r="AA19">
-        <v>0.02837906937105847</v>
+        <v>0.004133102545325433</v>
       </c>
       <c r="AB19">
-        <v>0.1363370919718991</v>
+        <v>0.1112219919783355</v>
       </c>
       <c r="AC19">
-        <v>-0.1079580226008406</v>
+        <v>-0.10708888943301</v>
       </c>
       <c r="AD19">
-        <v>0.078</v>
+        <v>4.58</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0.078</v>
+        <v>4.58</v>
       </c>
       <c r="AG19">
-        <v>-2.272</v>
+        <v>-22.52</v>
       </c>
       <c r="AH19">
-        <v>0.001132437062632481</v>
+        <v>0.009726469588854911</v>
       </c>
       <c r="AI19">
-        <v>0.005207637868874349</v>
+        <v>0.04608573153552023</v>
       </c>
       <c r="AJ19">
-        <v>-0.03415103415103416</v>
+        <v>-0.05074586506827708</v>
       </c>
       <c r="AK19">
-        <v>-0.1799176433322775</v>
+        <v>-0.3115661317100166</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>-4.95</v>
       </c>
       <c r="AN19">
-        <v>0.115727002967359</v>
+        <v>4.967462039045553</v>
+      </c>
+      <c r="AO19">
+        <v>0.2614035087719299</v>
       </c>
       <c r="AP19">
-        <v>-3.370919881305638</v>
+        <v>-24.42516268980478</v>
+      </c>
+      <c r="AQ19">
+        <v>-0.06020202020202019</v>
       </c>
     </row>
     <row r="20">
@@ -2856,7 +2907,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Osmanli Yatirim Menkul Degerler A.S. (IBSE:OSMEN)</t>
+          <t>Verusaturk Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:VERTU)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2865,112 +2916,121 @@
         </is>
       </c>
       <c r="D20">
-        <v>0.42</v>
+        <v>0.252</v>
       </c>
       <c r="E20">
-        <v>1.13</v>
+        <v>1.006</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>-0.0756164383561644</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>-0.0756164383561644</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>-0.07041095890410959</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>-0.07041095890410959</v>
       </c>
       <c r="K20">
-        <v>8.02</v>
+        <v>41.1</v>
       </c>
       <c r="L20">
-        <v>0.06098859315589353</v>
+        <v>11.26027397260274</v>
       </c>
       <c r="M20">
-        <v>0.297</v>
+        <v>2.205</v>
       </c>
       <c r="N20">
-        <v>0.004194915254237288</v>
+        <v>0.03516746411483253</v>
       </c>
       <c r="O20">
-        <v>0.03703241895261845</v>
+        <v>0.05364963503649635</v>
       </c>
       <c r="P20">
-        <v>0.297</v>
+        <v>0.285</v>
       </c>
       <c r="Q20">
-        <v>0.004194915254237288</v>
+        <v>0.004545454545454545</v>
       </c>
       <c r="R20">
-        <v>0.03703241895261845</v>
+        <v>0.006934306569343065</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>0.870748299319728</v>
       </c>
       <c r="U20">
-        <v>22.8</v>
+        <v>4.26</v>
       </c>
       <c r="V20">
-        <v>0.3220338983050848</v>
+        <v>0.06794258373205742</v>
       </c>
       <c r="W20">
-        <v>0.4717647058823529</v>
+        <v>0.3918017159199237</v>
       </c>
       <c r="X20">
-        <v>0.1521930649041999</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y20">
-        <v>0.319571640978153</v>
+        <v>0.2809145672962902</v>
       </c>
       <c r="Z20">
-        <v>12.28971962616822</v>
+        <v>0.03396739130434782</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>-0.002391676593210244</v>
       </c>
       <c r="AB20">
-        <v>0.1436950820907051</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC20">
-        <v>-0.1436950820907051</v>
+        <v>-0.1132788252168438</v>
       </c>
       <c r="AD20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>-7.800000000000001</v>
+        <v>-4.26</v>
       </c>
       <c r="AH20">
-        <v>0.1748251748251748</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>0.4901960784313725</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>-0.1238095238095238</v>
+        <v>-0.07289527720739218</v>
       </c>
       <c r="AK20">
-        <v>-1</v>
+        <v>-0.04040212443095599</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>0.803</v>
       </c>
       <c r="AM20">
-        <v>-1.99</v>
+        <v>0.641</v>
+      </c>
+      <c r="AN20">
+        <v>-0</v>
+      </c>
+      <c r="AO20">
+        <v>-0.3200498132004981</v>
+      </c>
+      <c r="AP20">
+        <v>19.36363636363636</v>
       </c>
       <c r="AQ20">
-        <v>-0</v>
+        <v>-0.4009360374414976</v>
       </c>
     </row>
     <row r="21">
@@ -2981,7 +3041,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ÜNLÜ Yatirim Holding A.S. (IBSE:UNLU)</t>
+          <t>Osmanli Yatirim Menkul Degerler A.S. (IBSE:OSMEN)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2989,6 +3049,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D21">
+        <v>0.753</v>
+      </c>
+      <c r="E21">
+        <v>2.044</v>
+      </c>
       <c r="G21">
         <v>0</v>
       </c>
@@ -3002,91 +3068,91 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>11.4</v>
+        <v>26.4</v>
       </c>
       <c r="L21">
-        <v>0.02406078514140988</v>
+        <v>0.07154471544715446</v>
       </c>
       <c r="M21">
-        <v>1.454</v>
+        <v>0.629</v>
       </c>
       <c r="N21">
-        <v>0.01511434511434511</v>
+        <v>0.00521558872305141</v>
       </c>
       <c r="O21">
-        <v>0.1275438596491228</v>
+        <v>0.02382575757575758</v>
       </c>
       <c r="P21">
-        <v>0.945</v>
+        <v>0.629</v>
       </c>
       <c r="Q21">
-        <v>0.009823284823284822</v>
+        <v>0.00521558872305141</v>
       </c>
       <c r="R21">
-        <v>0.08289473684210526</v>
+        <v>0.02382575757575758</v>
       </c>
       <c r="S21">
-        <v>0.509</v>
+        <v>0</v>
       </c>
       <c r="T21">
-        <v>0.3500687757909216</v>
+        <v>0</v>
       </c>
       <c r="U21">
-        <v>11.6</v>
+        <v>42.1</v>
       </c>
       <c r="V21">
-        <v>0.1205821205821206</v>
+        <v>0.3490878938640133</v>
       </c>
       <c r="W21">
-        <v>0.1890547263681592</v>
+        <v>1.692307692307692</v>
       </c>
       <c r="X21">
-        <v>0.1559531411314349</v>
+        <v>0.1156839924686142</v>
       </c>
       <c r="Y21">
-        <v>0.0331015852367243</v>
+        <v>1.576623699839078</v>
       </c>
       <c r="Z21">
-        <v>9.074889867841408</v>
+        <v>47.30769230769231</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.145689945451083</v>
+        <v>0.1138557459495408</v>
       </c>
       <c r="AC21">
-        <v>-0.145689945451083</v>
+        <v>-0.1138557459495408</v>
       </c>
       <c r="AD21">
-        <v>25.2</v>
+        <v>10.7</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>25.2</v>
+        <v>10.7</v>
       </c>
       <c r="AG21">
-        <v>13.6</v>
+        <v>-31.4</v>
       </c>
       <c r="AH21">
-        <v>0.2075782537067545</v>
+        <v>0.0814927646610815</v>
       </c>
       <c r="AI21">
-        <v>0.3766816143497758</v>
+        <v>0.2233820459290188</v>
       </c>
       <c r="AJ21">
-        <v>0.1238615664845173</v>
+        <v>-0.352017937219731</v>
       </c>
       <c r="AK21">
-        <v>0.2459312839059674</v>
+        <v>-5.413793103448276</v>
       </c>
       <c r="AL21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-17.9</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="AQ21">
         <v>-0</v>
@@ -3100,7 +3166,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Verusaturk Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:VERTU)</t>
+          <t>Yesil Yatirim Holding Anonim Sirketi (IBSE:YESIL)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3108,104 +3174,92 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="E22">
-        <v>1.811</v>
-      </c>
       <c r="K22">
-        <v>51.6</v>
+        <v>-3.29</v>
       </c>
       <c r="M22">
-        <v>0.281</v>
+        <v>-0</v>
       </c>
       <c r="N22">
-        <v>0.002345575959933222</v>
+        <v>-0</v>
       </c>
       <c r="O22">
-        <v>0.005445736434108527</v>
+        <v>0</v>
       </c>
       <c r="P22">
-        <v>0.281</v>
+        <v>-0</v>
       </c>
       <c r="Q22">
-        <v>0.002345575959933222</v>
+        <v>-0</v>
       </c>
       <c r="R22">
-        <v>0.005445736434108527</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <v>0</v>
       </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
       <c r="U22">
-        <v>0.004</v>
+        <v>0.111</v>
       </c>
       <c r="V22">
-        <v>3.33889816360601e-05</v>
+        <v>0.003908450704225352</v>
       </c>
       <c r="W22">
-        <v>0.4615384615384616</v>
+        <v>-0.1246212121212121</v>
       </c>
       <c r="X22">
-        <v>0.1378932143151368</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y22">
-        <v>0.3236452472233248</v>
+        <v>-0.2355083607448457</v>
       </c>
       <c r="Z22">
         <v>0</v>
       </c>
       <c r="AA22">
-        <v>-0.01106659689277411</v>
+        <v>-0.005265350960263647</v>
       </c>
       <c r="AB22">
-        <v>0.1371754140174368</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC22">
-        <v>-0.1482420109102109</v>
+        <v>-0.1161524995838972</v>
       </c>
       <c r="AD22">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AG22">
-        <v>2.556</v>
+        <v>-0.111</v>
       </c>
       <c r="AH22">
-        <v>0.02092186989212161</v>
+        <v>0</v>
       </c>
       <c r="AI22">
-        <v>0.02382281779266704</v>
+        <v>0</v>
       </c>
       <c r="AJ22">
-        <v>0.0208898623688254</v>
+        <v>-0.003923786630845912</v>
       </c>
       <c r="AK22">
-        <v>0.02378648004764741</v>
+        <v>-0.007660984194906482</v>
       </c>
       <c r="AL22">
-        <v>0.631</v>
+        <v>0.017</v>
       </c>
       <c r="AM22">
-        <v>0.611</v>
-      </c>
-      <c r="AN22">
-        <v>-2</v>
+        <v>0.003000000000000001</v>
       </c>
       <c r="AO22">
-        <v>-2.044374009508716</v>
-      </c>
-      <c r="AP22">
-        <v>-1.996875</v>
+        <v>-8.176470588235293</v>
       </c>
       <c r="AQ22">
-        <v>-2.111292962356792</v>
+        <v>-46.33333333333332</v>
       </c>
     </row>
     <row r="23">
@@ -3216,7 +3270,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Info Yatirim Menkul Degerler A.S. (IBSE:INFO)</t>
+          <t>Denge Yatirim Holding A.S. (IBSE:DENGE)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3224,29 +3278,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D23">
-        <v>0.256</v>
-      </c>
-      <c r="E23">
-        <v>2.076</v>
-      </c>
       <c r="G23">
-        <v>0</v>
+        <v>0.1364016736401674</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>0.1364016736401674</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>0.02439330543933054</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>0.01664533011843132</v>
       </c>
       <c r="K23">
-        <v>19.7</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L23">
-        <v>0.03512212515599929</v>
+        <v>0.4092050209205021</v>
       </c>
       <c r="M23">
         <v>-0</v>
@@ -3270,64 +3318,73 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>37.2</v>
+        <v>1.88</v>
       </c>
       <c r="V23">
-        <v>0.2563749138525155</v>
+        <v>0.08281938325991189</v>
       </c>
       <c r="W23">
-        <v>0.7975708502024291</v>
+        <v>0.2868035190615835</v>
       </c>
       <c r="X23">
-        <v>0.1658811993714438</v>
+        <v>0.1494712391865035</v>
       </c>
       <c r="Y23">
-        <v>0.6316896508309854</v>
+        <v>0.13733227987508</v>
       </c>
       <c r="Z23">
-        <v>29.99465240641711</v>
+        <v>0.5642115203021717</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>0.009391487012051662</v>
       </c>
       <c r="AB23">
-        <v>0.1482669368881177</v>
+        <v>0.1260575703328908</v>
       </c>
       <c r="AC23">
-        <v>-0.1482669368881177</v>
+        <v>-0.1166660833208391</v>
       </c>
       <c r="AD23">
-        <v>57.2</v>
+        <v>16.2</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>57.2</v>
+        <v>16.2</v>
       </c>
       <c r="AG23">
-        <v>20</v>
+        <v>14.32</v>
       </c>
       <c r="AH23">
-        <v>0.2827483934750371</v>
+        <v>0.416452442159383</v>
       </c>
       <c r="AI23">
-        <v>0.6434195725534309</v>
+        <v>0.2301136363636363</v>
       </c>
       <c r="AJ23">
-        <v>0.1211387038158692</v>
+        <v>0.3868179362506753</v>
       </c>
       <c r="AK23">
-        <v>0.3868471953578336</v>
+        <v>0.208990075890251</v>
       </c>
       <c r="AL23">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="AM23">
-        <v>-9.869999999999999</v>
+        <v>-28.71</v>
+      </c>
+      <c r="AN23">
+        <v>13.96551724137931</v>
+      </c>
+      <c r="AO23">
+        <v>0.1670487106017192</v>
+      </c>
+      <c r="AP23">
+        <v>12.3448275862069</v>
       </c>
       <c r="AQ23">
-        <v>-0</v>
+        <v>-0.02030651340996168</v>
       </c>
     </row>
     <row r="24">
@@ -3338,7 +3395,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hedef Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HDFGS)</t>
+          <t>ÜNLÜ Yatirim Holding A.S. (IBSE:UNLU)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3346,101 +3403,107 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
       <c r="K24">
-        <v>-1.1</v>
+        <v>16.2</v>
+      </c>
+      <c r="L24">
+        <v>0.02194824549519035</v>
       </c>
       <c r="M24">
-        <v>2.14</v>
+        <v>2.233</v>
       </c>
       <c r="N24">
-        <v>0.03375394321766562</v>
+        <v>0.02398496240601504</v>
       </c>
       <c r="O24">
-        <v>-1.945454545454545</v>
+        <v>0.1378395061728395</v>
       </c>
       <c r="P24">
-        <v>-0</v>
+        <v>1.82</v>
       </c>
       <c r="Q24">
-        <v>-0</v>
+        <v>0.01954887218045113</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>0.1123456790123457</v>
       </c>
       <c r="S24">
-        <v>2.14</v>
+        <v>0.413</v>
       </c>
       <c r="T24">
-        <v>1</v>
+        <v>0.1849529780564263</v>
       </c>
       <c r="U24">
-        <v>0.011</v>
+        <v>38.2</v>
       </c>
       <c r="V24">
-        <v>0.0001735015772870662</v>
+        <v>0.41031149301826</v>
       </c>
       <c r="W24">
-        <v>-0.01361386138613862</v>
+        <v>0.3884892086330935</v>
       </c>
       <c r="X24">
-        <v>0.1363376642142887</v>
+        <v>0.1333030772235712</v>
       </c>
       <c r="Y24">
-        <v>-0.1499515256004273</v>
+        <v>0.2551861314095223</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>13.7397617274758</v>
       </c>
       <c r="AA24">
-        <v>-0.01195922019331342</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>0.1363164969013344</v>
+        <v>0.1215637682386012</v>
       </c>
       <c r="AC24">
-        <v>-0.1482757170946478</v>
+        <v>-0.1215637682386012</v>
       </c>
       <c r="AD24">
-        <v>0.041</v>
+        <v>38.6</v>
       </c>
       <c r="AE24">
         <v>0</v>
       </c>
       <c r="AF24">
-        <v>0.041</v>
+        <v>38.6</v>
       </c>
       <c r="AG24">
-        <v>0.03</v>
+        <v>0.3999999999999986</v>
       </c>
       <c r="AH24">
-        <v>0.0006462697624564557</v>
+        <v>0.2930903568716781</v>
       </c>
       <c r="AI24">
-        <v>0.001153597253875805</v>
+        <v>0.4667472793228537</v>
       </c>
       <c r="AJ24">
-        <v>0.0004729623206684534</v>
+        <v>0.004278074866310145</v>
       </c>
       <c r="AK24">
-        <v>0.0008443568815085843</v>
+        <v>0.008988764044943788</v>
       </c>
       <c r="AL24">
-        <v>0.199</v>
+        <v>0</v>
       </c>
       <c r="AM24">
-        <v>0.199</v>
-      </c>
-      <c r="AN24">
-        <v>-0.04371002132196163</v>
-      </c>
-      <c r="AO24">
-        <v>-4.768844221105527</v>
-      </c>
-      <c r="AP24">
-        <v>-0.03198294243070363</v>
+        <v>-15.1</v>
       </c>
       <c r="AQ24">
-        <v>-4.768844221105527</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="25">
@@ -3451,7 +3514,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Verusa Holding A.S. (IBSE:VERUS)</t>
+          <t>Info Yatirim Menkul Degerler A.S. (IBSE:INFO)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3460,121 +3523,115 @@
         </is>
       </c>
       <c r="D25">
-        <v>0.327</v>
+        <v>0.289</v>
       </c>
       <c r="E25">
-        <v>0.797</v>
+        <v>2.029</v>
       </c>
       <c r="G25">
-        <v>-0.2368983957219251</v>
+        <v>0</v>
       </c>
       <c r="H25">
-        <v>-0.2368983957219251</v>
+        <v>0</v>
       </c>
       <c r="I25">
-        <v>-0.05828877005347594</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>-0.05363336333633364</v>
+        <v>0</v>
       </c>
       <c r="K25">
-        <v>19.8</v>
+        <v>27.2</v>
       </c>
       <c r="L25">
-        <v>1.058823529411765</v>
+        <v>0.1452215696743193</v>
       </c>
       <c r="M25">
-        <v>4.429</v>
+        <v>8.32</v>
       </c>
       <c r="N25">
-        <v>0.01081298828125</v>
+        <v>0.08577319587628866</v>
       </c>
       <c r="O25">
-        <v>0.2236868686868687</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="P25">
-        <v>0.129</v>
+        <v>8.32</v>
       </c>
       <c r="Q25">
-        <v>0.00031494140625</v>
+        <v>0.08577319587628866</v>
       </c>
       <c r="R25">
-        <v>0.006515151515151515</v>
+        <v>0.3058823529411765</v>
       </c>
       <c r="S25">
-        <v>4.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>0.9708737864077671</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>4.74</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="V25">
-        <v>0.011572265625</v>
+        <v>0.8927835051546391</v>
       </c>
       <c r="W25">
-        <v>0.2780898876404495</v>
+        <v>0.8580441640378549</v>
       </c>
       <c r="X25">
-        <v>0.13819510800398</v>
+        <v>0.1546410751722566</v>
       </c>
       <c r="Y25">
-        <v>0.1398947796364694</v>
+        <v>0.7034030888655983</v>
       </c>
       <c r="Z25">
-        <v>0.2331089503864373</v>
+        <v>3.622823984526112</v>
       </c>
       <c r="AA25">
-        <v>-0.01250241703302716</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>0.1373380859805351</v>
+        <v>0.1271810384806464</v>
       </c>
       <c r="AC25">
-        <v>-0.1498405030135622</v>
+        <v>-0.1271810384806464</v>
       </c>
       <c r="AD25">
-        <v>10.4</v>
+        <v>78.5</v>
       </c>
       <c r="AE25">
         <v>0</v>
       </c>
       <c r="AF25">
-        <v>10.4</v>
+        <v>78.5</v>
       </c>
       <c r="AG25">
-        <v>5.66</v>
+        <v>-8.099999999999994</v>
       </c>
       <c r="AH25">
-        <v>0.02476190476190476</v>
+        <v>0.4472934472934473</v>
       </c>
       <c r="AI25">
-        <v>0.1125541125541125</v>
+        <v>0.6596638655462185</v>
       </c>
       <c r="AJ25">
-        <v>0.01363001493040505</v>
+        <v>-0.0911136107986501</v>
       </c>
       <c r="AK25">
-        <v>0.0645676477298654</v>
+        <v>-0.2499999999999998</v>
       </c>
       <c r="AL25">
-        <v>0.994</v>
+        <v>1.06</v>
       </c>
       <c r="AM25">
-        <v>-0.226</v>
-      </c>
-      <c r="AN25">
-        <v>-13.90374331550802</v>
+        <v>1.06</v>
       </c>
       <c r="AO25">
-        <v>-1.096579476861167</v>
-      </c>
-      <c r="AP25">
-        <v>-7.566844919786097</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>4.823008849557523</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -3585,7 +3642,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Denge Yatirim Holding A.S. (IBSE:DENGE)</t>
+          <t>Dagi Yatirim Holding A.S. (IBSE:DAGHL)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3593,23 +3650,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D26">
+        <v>1.628</v>
+      </c>
       <c r="G26">
-        <v>-0.07049999999999999</v>
+        <v>0.0365034965034965</v>
       </c>
       <c r="H26">
-        <v>-0.07049999999999999</v>
+        <v>0.0365034965034965</v>
       </c>
       <c r="I26">
-        <v>-0.0495</v>
+        <v>-0.003356643356643357</v>
       </c>
       <c r="J26">
-        <v>-0.04244290540540541</v>
+        <v>-0.003076923076923077</v>
       </c>
       <c r="K26">
-        <v>13.1</v>
+        <v>0.989</v>
       </c>
       <c r="L26">
-        <v>0.655</v>
+        <v>0.06916083916083916</v>
       </c>
       <c r="M26">
         <v>-0</v>
@@ -3633,73 +3693,73 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>9.220000000000001</v>
+        <v>0.023</v>
       </c>
       <c r="V26">
-        <v>0.1893223819301848</v>
+        <v>0.001769230769230769</v>
       </c>
       <c r="W26">
-        <v>0.2176079734219269</v>
+        <v>1.306472919418758</v>
       </c>
       <c r="X26">
-        <v>0.1695835556192742</v>
+        <v>0.1116107926925093</v>
       </c>
       <c r="Y26">
-        <v>0.04802441780265268</v>
+        <v>1.194862126726249</v>
       </c>
       <c r="Z26">
-        <v>0.2531645569620253</v>
+        <v>6.598984771573604</v>
       </c>
       <c r="AA26">
-        <v>-0.01074503934314061</v>
+        <v>-0.02030456852791878</v>
       </c>
       <c r="AB26">
-        <v>0.1502040994027945</v>
+        <v>0.1113682801658467</v>
       </c>
       <c r="AC26">
-        <v>-0.1609491387459351</v>
+        <v>-0.1316728486937655</v>
       </c>
       <c r="AD26">
-        <v>21.6</v>
+        <v>0.174</v>
       </c>
       <c r="AE26">
         <v>0</v>
       </c>
       <c r="AF26">
-        <v>21.6</v>
+        <v>0.174</v>
       </c>
       <c r="AG26">
-        <v>12.38</v>
+        <v>0.151</v>
       </c>
       <c r="AH26">
-        <v>0.3072546230440967</v>
+        <v>0.01320783361165933</v>
       </c>
       <c r="AI26">
-        <v>0.3</v>
+        <v>0.1078066914498141</v>
       </c>
       <c r="AJ26">
-        <v>0.2026850032743942</v>
+        <v>0.01148201657668618</v>
       </c>
       <c r="AK26">
-        <v>0.1971965594138261</v>
+        <v>0.09490886235072281</v>
       </c>
       <c r="AL26">
-        <v>2.78</v>
+        <v>0.354</v>
       </c>
       <c r="AM26">
-        <v>-32.62</v>
+        <v>-1.766</v>
       </c>
       <c r="AN26">
-        <v>-26.63378545006165</v>
+        <v>17.4</v>
       </c>
       <c r="AO26">
-        <v>-0.3561151079136691</v>
+        <v>-0.1355932203389831</v>
       </c>
       <c r="AP26">
-        <v>-15.26510480887793</v>
+        <v>15.1</v>
       </c>
       <c r="AQ26">
-        <v>0.03034947884733293</v>
+        <v>0.02718006795016988</v>
       </c>
     </row>
     <row r="27">
@@ -3710,7 +3770,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Gozde Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:GOZDE)</t>
+          <t>Hub Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HUBVC)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3718,29 +3778,23 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D27">
-        <v>-0.46</v>
-      </c>
-      <c r="E27">
-        <v>1.38</v>
-      </c>
       <c r="G27">
-        <v>-139.2</v>
+        <v>-2.729411764705882</v>
       </c>
       <c r="H27">
-        <v>-139.2</v>
+        <v>-2.729411764705882</v>
       </c>
       <c r="I27">
-        <v>-636</v>
+        <v>-2.311764705882353</v>
       </c>
       <c r="J27">
-        <v>-636</v>
+        <v>-2.311764705882353</v>
       </c>
       <c r="K27">
-        <v>316.8</v>
+        <v>3.7</v>
       </c>
       <c r="L27">
-        <v>12672</v>
+        <v>21.76470588235294</v>
       </c>
       <c r="M27">
         <v>-0</v>
@@ -3764,73 +3818,73 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>0.03683333333333334</v>
       </c>
       <c r="W27">
-        <v>0.4267816246800485</v>
+        <v>0.3363636363636364</v>
       </c>
       <c r="X27">
-        <v>0.1512435953330112</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="Y27">
-        <v>0.2755380293470373</v>
+        <v>0.2254764877400028</v>
       </c>
       <c r="Z27">
-        <v>2.896555879197399e-05</v>
+        <v>0.01552369646607616</v>
       </c>
       <c r="AA27">
-        <v>-0.01842209539169546</v>
+        <v>-0.03588713359510547</v>
       </c>
       <c r="AB27">
-        <v>0.1433263930270297</v>
+        <v>0.1108871486236336</v>
       </c>
       <c r="AC27">
-        <v>-0.1617484884187252</v>
+        <v>-0.1467742822187391</v>
       </c>
       <c r="AD27">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AE27">
         <v>0</v>
       </c>
       <c r="AF27">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>86.40000000000001</v>
+        <v>-0.663</v>
       </c>
       <c r="AH27">
-        <v>0.1661218996346857</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>0.1138189961796865</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>0.1661218996346857</v>
+        <v>-0.03824191036511507</v>
       </c>
       <c r="AK27">
-        <v>0.1138189961796865</v>
+        <v>-0.05848107965070125</v>
       </c>
       <c r="AL27">
-        <v>18.5</v>
+        <v>0.003</v>
       </c>
       <c r="AM27">
-        <v>18.5</v>
+        <v>-0.011</v>
       </c>
       <c r="AN27">
-        <v>-5.433962264150944</v>
+        <v>-0</v>
       </c>
       <c r="AO27">
-        <v>-0.8594594594594595</v>
+        <v>-131</v>
       </c>
       <c r="AP27">
-        <v>-5.433962264150944</v>
+        <v>1.678481012658228</v>
       </c>
       <c r="AQ27">
-        <v>-0.8594594594594595</v>
+        <v>35.72727272727273</v>
       </c>
     </row>
     <row r="28">
@@ -3841,7 +3895,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Yesil Yatirim Holding Anonim Sirketi (IBSE:YESIL)</t>
+          <t>Gozde Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:GOZDE)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3849,8 +3903,29 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D28">
+        <v>0.362</v>
+      </c>
+      <c r="E28">
+        <v>0.62</v>
+      </c>
+      <c r="G28">
+        <v>-1.743682310469314</v>
+      </c>
+      <c r="H28">
+        <v>-1.743682310469314</v>
+      </c>
+      <c r="I28">
+        <v>-20.28880866425993</v>
+      </c>
+      <c r="J28">
+        <v>-20.28880866425993</v>
+      </c>
       <c r="K28">
-        <v>-0.574</v>
+        <v>212.8</v>
+      </c>
+      <c r="L28">
+        <v>76.82310469314079</v>
       </c>
       <c r="M28">
         <v>-0</v>
@@ -3859,7 +3934,7 @@
         <v>-0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P28">
         <v>-0</v>
@@ -3868,73 +3943,79 @@
         <v>-0</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S28">
         <v>0</v>
       </c>
       <c r="U28">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="V28">
-        <v>1.6e-05</v>
+        <v>7.377351530800442e-06</v>
       </c>
       <c r="W28">
-        <v>-0.01019538188277087</v>
+        <v>0.3163371488033299</v>
       </c>
       <c r="X28">
-        <v>0.1362891195533376</v>
+        <v>0.1275395192711992</v>
       </c>
       <c r="Y28">
-        <v>-0.1464845014361085</v>
+        <v>0.1887976295321306</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>0.003649058095112633</v>
       </c>
       <c r="AA28">
-        <v>-0.02834702536787939</v>
+        <v>-0.07403504149650902</v>
       </c>
       <c r="AB28">
-        <v>0.1362891195533376</v>
+        <v>0.1189936637110427</v>
       </c>
       <c r="AC28">
-        <v>-0.164636144921217</v>
+        <v>-0.1930287052075517</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>83.5</v>
       </c>
       <c r="AE28">
         <v>0</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>83.5</v>
       </c>
       <c r="AG28">
-        <v>-0.001</v>
+        <v>83.498</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>0.2354765933446136</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>0.1111998934611799</v>
       </c>
       <c r="AJ28">
-        <v>-1.600025600409606e-05</v>
+        <v>0.2354722812875425</v>
       </c>
       <c r="AK28">
-        <v>-3.788022273570969e-05</v>
+        <v>0.1111975261620087</v>
       </c>
       <c r="AL28">
-        <v>0.002</v>
+        <v>21.2</v>
       </c>
       <c r="AM28">
-        <v>-0.047</v>
+        <v>21.177</v>
+      </c>
+      <c r="AN28">
+        <v>-1.48576512455516</v>
       </c>
       <c r="AO28">
-        <v>-785</v>
+        <v>-2.650943396226416</v>
+      </c>
+      <c r="AP28">
+        <v>-1.485729537366548</v>
       </c>
       <c r="AQ28">
-        <v>33.40425531914894</v>
+        <v>-2.653822543325306</v>
       </c>
     </row>
     <row r="29">
@@ -3945,7 +4026,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hub Girisim Sermayesi Yatirim Ortakligi A.S. (IBSE:HUBVC)</t>
+          <t>Marka Yatirim Holding A.S. (IBSE:MARKA)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3954,28 +4035,28 @@
         </is>
       </c>
       <c r="D29">
-        <v>-0.58</v>
+        <v>0.423</v>
       </c>
       <c r="E29">
-        <v>1.628</v>
+        <v>-0.379</v>
       </c>
       <c r="G29">
-        <v>-205.5</v>
+        <v>0.7021013597033373</v>
       </c>
       <c r="H29">
-        <v>-205.5</v>
+        <v>0.7021013597033373</v>
       </c>
       <c r="I29">
-        <v>-235.5</v>
+        <v>-0.06180469715698393</v>
       </c>
       <c r="J29">
-        <v>-235.5</v>
+        <v>-0.06180469715698393</v>
       </c>
       <c r="K29">
-        <v>5.62</v>
+        <v>0.055</v>
       </c>
       <c r="L29">
-        <v>2810</v>
+        <v>0.06798516687268231</v>
       </c>
       <c r="M29">
         <v>-0</v>
@@ -3999,73 +4080,73 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>0.053</v>
+        <v>0.067</v>
       </c>
       <c r="V29">
-        <v>0.004690265486725663</v>
+        <v>0.002887931034482759</v>
       </c>
       <c r="W29">
-        <v>0.5752302968270215</v>
+        <v>0.05092592592592592</v>
       </c>
       <c r="X29">
-        <v>0.1363156918089327</v>
+        <v>0.1108941398341682</v>
       </c>
       <c r="Y29">
-        <v>0.4389146050180888</v>
+        <v>-0.05996821390824229</v>
       </c>
       <c r="Z29">
-        <v>0.0002104598547827002</v>
+        <v>1.651020408163265</v>
       </c>
       <c r="AA29">
-        <v>-0.04956329580132589</v>
+        <v>-0.1020408163265306</v>
       </c>
       <c r="AB29">
-        <v>0.1363051450684522</v>
+        <v>0.1108918584983504</v>
       </c>
       <c r="AC29">
-        <v>-0.1858684408697781</v>
+        <v>-0.212932674824881</v>
       </c>
       <c r="AD29">
+        <v>0.003</v>
+      </c>
+      <c r="AE29">
+        <v>0</v>
+      </c>
+      <c r="AF29">
+        <v>0.003</v>
+      </c>
+      <c r="AG29">
+        <v>-0.064</v>
+      </c>
+      <c r="AH29">
+        <v>0.0001292936258242469</v>
+      </c>
+      <c r="AI29">
+        <v>0.003181336161187699</v>
+      </c>
+      <c r="AJ29">
+        <v>-0.002766251728907331</v>
+      </c>
+      <c r="AK29">
+        <v>-0.07305936073059362</v>
+      </c>
+      <c r="AL29">
         <v>0.004</v>
       </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0.004</v>
-      </c>
-      <c r="AG29">
-        <v>-0.049</v>
-      </c>
-      <c r="AH29">
-        <v>0.0003538570417551309</v>
-      </c>
-      <c r="AI29">
-        <v>0.0003635041802980735</v>
-      </c>
-      <c r="AJ29">
-        <v>-0.004355168429472935</v>
-      </c>
-      <c r="AK29">
-        <v>-0.004474477216692539</v>
-      </c>
-      <c r="AL29">
-        <v>0.003</v>
-      </c>
       <c r="AM29">
-        <v>-0.008</v>
+        <v>-0.09899999999999999</v>
       </c>
       <c r="AN29">
-        <v>-0.008438818565400845</v>
+        <v>-0.1875</v>
       </c>
       <c r="AO29">
-        <v>-157</v>
+        <v>-12.5</v>
       </c>
       <c r="AP29">
-        <v>0.1033755274261604</v>
+        <v>4</v>
       </c>
       <c r="AQ29">
-        <v>58.87499999999999</v>
+        <v>0.5050505050505051</v>
       </c>
     </row>
   </sheetData>
